--- a/cis_xccdf/rhel-9-cis-stig-compare.xlsx
+++ b/cis_xccdf/rhel-9-cis-stig-compare.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://frbprod1-my.sharepoint.com/personal/brandon_field_frit_frb_org/Documents/Documents/GitHub/Sandbox/cis_xccdf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="294" documentId="11_57A1F0955358560E62355476585DCE3A874B2B05" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB0119DE-27C2-244A-AD64-A79AA8F92A4E}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="11_57A1F0955358560E62355476585DCE3A874B2B05" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA80927B-F798-D744-B579-56470C215967}"/>
   <bookViews>
     <workbookView xWindow="74400" yWindow="-1340" windowWidth="38400" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14516,7 +14516,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H654"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -14552,7 +14551,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="320" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
@@ -14578,7 +14577,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="320" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
@@ -14602,7 +14601,7 @@
       </c>
       <c r="H3"/>
     </row>
-    <row r="4" spans="1:8" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="320" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
@@ -14628,7 +14627,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="320" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>7</v>
       </c>
@@ -14654,7 +14653,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="320" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>7</v>
       </c>
@@ -14680,7 +14679,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="320" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
@@ -14706,7 +14705,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="320" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>7</v>
       </c>
@@ -14732,7 +14731,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="320" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>7</v>
       </c>
@@ -14758,7 +14757,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="335" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>7</v>
       </c>
@@ -14784,7 +14783,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="335" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>7</v>
       </c>
@@ -14810,7 +14809,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="335" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>7</v>
       </c>
@@ -14836,7 +14835,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="320" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>7</v>
       </c>
@@ -14860,7 +14859,7 @@
       </c>
       <c r="H13"/>
     </row>
-    <row r="14" spans="1:8" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="320" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>7</v>
       </c>
@@ -14884,7 +14883,7 @@
       </c>
       <c r="H14"/>
     </row>
-    <row r="15" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>7</v>
       </c>
@@ -14908,7 +14907,7 @@
       </c>
       <c r="H15"/>
     </row>
-    <row r="16" spans="1:8" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="240" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>7</v>
       </c>
@@ -14934,7 +14933,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>7</v>
       </c>
@@ -14960,7 +14959,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="240" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>7</v>
       </c>
@@ -14986,7 +14985,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>7</v>
       </c>
@@ -15012,7 +15011,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="350" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="350" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
         <v>7</v>
       </c>
@@ -15036,7 +15035,7 @@
       </c>
       <c r="H20"/>
     </row>
-    <row r="21" spans="1:8" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
         <v>7</v>
       </c>
@@ -15060,7 +15059,7 @@
       </c>
       <c r="H21"/>
     </row>
-    <row r="22" spans="1:8" ht="380" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="380" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
         <v>7</v>
       </c>
@@ -15086,7 +15085,7 @@
         <v>2643</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="128" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="128" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
         <v>7</v>
       </c>
@@ -15112,7 +15111,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
         <v>7</v>
       </c>
@@ -15138,7 +15137,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
         <v>7</v>
       </c>
@@ -15162,7 +15161,7 @@
       </c>
       <c r="H25"/>
     </row>
-    <row r="26" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>65</v>
       </c>
@@ -15188,7 +15187,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" ht="160" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>7</v>
       </c>
@@ -15212,7 +15211,7 @@
       </c>
       <c r="H27"/>
     </row>
-    <row r="28" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
         <v>7</v>
       </c>
@@ -15236,7 +15235,7 @@
       </c>
       <c r="H28"/>
     </row>
-    <row r="29" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
         <v>65</v>
       </c>
@@ -15262,7 +15261,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
         <v>7</v>
       </c>
@@ -15288,7 +15287,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
         <v>7</v>
       </c>
@@ -15314,7 +15313,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
         <v>65</v>
       </c>
@@ -15338,7 +15337,7 @@
       </c>
       <c r="H32"/>
     </row>
-    <row r="33" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
         <v>7</v>
       </c>
@@ -15362,7 +15361,7 @@
       </c>
       <c r="H33"/>
     </row>
-    <row r="34" spans="1:8" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" ht="112" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
         <v>7</v>
       </c>
@@ -15388,7 +15387,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
         <v>7</v>
       </c>
@@ -15412,7 +15411,7 @@
       </c>
       <c r="H35"/>
     </row>
-    <row r="36" spans="1:8" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" ht="112" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
         <v>7</v>
       </c>
@@ -15436,7 +15435,7 @@
       </c>
       <c r="H36"/>
     </row>
-    <row r="37" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
         <v>7</v>
       </c>
@@ -15460,7 +15459,7 @@
       </c>
       <c r="H37"/>
     </row>
-    <row r="38" spans="1:8" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" ht="288" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
         <v>7</v>
       </c>
@@ -15484,7 +15483,7 @@
       </c>
       <c r="H38"/>
     </row>
-    <row r="39" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
         <v>7</v>
       </c>
@@ -15510,7 +15509,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
         <v>7</v>
       </c>
@@ -15536,7 +15535,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="128" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" ht="128" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
         <v>7</v>
       </c>
@@ -15560,7 +15559,7 @@
       </c>
       <c r="H41"/>
     </row>
-    <row r="42" spans="1:8" ht="128" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" ht="128" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
         <v>7</v>
       </c>
@@ -15584,7 +15583,7 @@
       </c>
       <c r="H42"/>
     </row>
-    <row r="43" spans="1:8" ht="128" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" ht="128" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
         <v>7</v>
       </c>
@@ -15608,7 +15607,7 @@
       </c>
       <c r="H43"/>
     </row>
-    <row r="44" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
         <v>7</v>
       </c>
@@ -15632,7 +15631,7 @@
       </c>
       <c r="H44"/>
     </row>
-    <row r="45" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
         <v>7</v>
       </c>
@@ -15656,7 +15655,7 @@
       </c>
       <c r="H45"/>
     </row>
-    <row r="46" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
         <v>7</v>
       </c>
@@ -15680,7 +15679,7 @@
       </c>
       <c r="H46"/>
     </row>
-    <row r="47" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
         <v>7</v>
       </c>
@@ -15704,7 +15703,7 @@
       </c>
       <c r="H47"/>
     </row>
-    <row r="48" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
         <v>7</v>
       </c>
@@ -15728,7 +15727,7 @@
       </c>
       <c r="H48"/>
     </row>
-    <row r="49" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
         <v>7</v>
       </c>
@@ -15752,7 +15751,7 @@
       </c>
       <c r="H49"/>
     </row>
-    <row r="50" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
         <v>7</v>
       </c>
@@ -15776,7 +15775,7 @@
       </c>
       <c r="H50"/>
     </row>
-    <row r="51" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
         <v>7</v>
       </c>
@@ -15800,7 +15799,7 @@
       </c>
       <c r="H51"/>
     </row>
-    <row r="52" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
         <v>7</v>
       </c>
@@ -15824,7 +15823,7 @@
       </c>
       <c r="H52"/>
     </row>
-    <row r="53" spans="1:8" ht="304" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" ht="304" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
         <v>7</v>
       </c>
@@ -15850,7 +15849,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
         <v>65</v>
       </c>
@@ -15874,7 +15873,7 @@
       </c>
       <c r="H54"/>
     </row>
-    <row r="55" spans="1:8" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" ht="240" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
         <v>7</v>
       </c>
@@ -15900,7 +15899,7 @@
         <v>2646</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
         <v>7</v>
       </c>
@@ -15924,7 +15923,7 @@
       </c>
       <c r="H56"/>
     </row>
-    <row r="57" spans="1:8" ht="80" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
         <v>7</v>
       </c>
@@ -15948,7 +15947,7 @@
       </c>
       <c r="H57"/>
     </row>
-    <row r="58" spans="1:8" ht="80" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
         <v>7</v>
       </c>
@@ -15972,7 +15971,7 @@
       </c>
       <c r="H58"/>
     </row>
-    <row r="59" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
         <v>65</v>
       </c>
@@ -15998,7 +15997,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
         <v>7</v>
       </c>
@@ -16022,7 +16021,7 @@
       </c>
       <c r="H60"/>
     </row>
-    <row r="61" spans="1:8" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" ht="256" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
         <v>7</v>
       </c>
@@ -16046,7 +16045,7 @@
       </c>
       <c r="H61"/>
     </row>
-    <row r="62" spans="1:8" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" ht="272" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
         <v>7</v>
       </c>
@@ -16072,7 +16071,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" ht="335" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
         <v>7</v>
       </c>
@@ -16096,7 +16095,7 @@
       </c>
       <c r="H63"/>
     </row>
-    <row r="64" spans="1:8" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" ht="240" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
         <v>7</v>
       </c>
@@ -16120,7 +16119,7 @@
       </c>
       <c r="H64"/>
     </row>
-    <row r="65" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
         <v>7</v>
       </c>
@@ -16144,7 +16143,7 @@
       </c>
       <c r="H65"/>
     </row>
-    <row r="66" spans="1:8" ht="80" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
         <v>7</v>
       </c>
@@ -16168,7 +16167,7 @@
       </c>
       <c r="H66"/>
     </row>
-    <row r="67" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="s">
         <v>7</v>
       </c>
@@ -16192,7 +16191,7 @@
       </c>
       <c r="H67"/>
     </row>
-    <row r="68" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
         <v>7</v>
       </c>
@@ -16216,7 +16215,7 @@
       </c>
       <c r="H68"/>
     </row>
-    <row r="69" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="s">
         <v>7</v>
       </c>
@@ -16240,7 +16239,7 @@
       </c>
       <c r="H69"/>
     </row>
-    <row r="70" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A70" s="7" t="s">
         <v>7</v>
       </c>
@@ -16264,7 +16263,7 @@
       </c>
       <c r="H70"/>
     </row>
-    <row r="71" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A71" s="7" t="s">
         <v>7</v>
       </c>
@@ -16288,7 +16287,7 @@
       </c>
       <c r="H71"/>
     </row>
-    <row r="72" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="s">
         <v>7</v>
       </c>
@@ -16312,7 +16311,7 @@
       </c>
       <c r="H72"/>
     </row>
-    <row r="73" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
         <v>7</v>
       </c>
@@ -16338,7 +16337,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="128" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" ht="128" x14ac:dyDescent="0.2">
       <c r="A74" s="7" t="s">
         <v>7</v>
       </c>
@@ -16362,7 +16361,7 @@
       </c>
       <c r="H74"/>
     </row>
-    <row r="75" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A75" s="7" t="s">
         <v>7</v>
       </c>
@@ -16388,7 +16387,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A76" s="7" t="s">
         <v>7</v>
       </c>
@@ -16414,7 +16413,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A77" s="7" t="s">
         <v>7</v>
       </c>
@@ -16438,7 +16437,7 @@
       </c>
       <c r="H77"/>
     </row>
-    <row r="78" spans="1:8" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A78" s="7" t="s">
         <v>7</v>
       </c>
@@ -16462,7 +16461,7 @@
       </c>
       <c r="H78"/>
     </row>
-    <row r="79" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A79" s="7" t="s">
         <v>7</v>
       </c>
@@ -16538,7 +16537,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A82" s="7" t="s">
         <v>7</v>
       </c>
@@ -16562,7 +16561,7 @@
       </c>
       <c r="H82"/>
     </row>
-    <row r="83" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A83" s="7" t="s">
         <v>7</v>
       </c>
@@ -16612,7 +16611,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="380" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" ht="380" x14ac:dyDescent="0.2">
       <c r="A85" s="7" t="s">
         <v>7</v>
       </c>
@@ -16636,7 +16635,7 @@
       </c>
       <c r="H85"/>
     </row>
-    <row r="86" spans="1:8" ht="395" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" ht="395" x14ac:dyDescent="0.2">
       <c r="A86" s="7" t="s">
         <v>7</v>
       </c>
@@ -16660,7 +16659,7 @@
       </c>
       <c r="H86"/>
     </row>
-    <row r="87" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A87" s="7" t="s">
         <v>7</v>
       </c>
@@ -16684,7 +16683,7 @@
       </c>
       <c r="H87"/>
     </row>
-    <row r="88" spans="1:8" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" ht="335" x14ac:dyDescent="0.2">
       <c r="A88" s="7" t="s">
         <v>7</v>
       </c>
@@ -16708,7 +16707,7 @@
       </c>
       <c r="H88"/>
     </row>
-    <row r="89" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A89" s="7" t="s">
         <v>7</v>
       </c>
@@ -16734,7 +16733,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A90" s="7" t="s">
         <v>65</v>
       </c>
@@ -16758,7 +16757,7 @@
       </c>
       <c r="H90"/>
     </row>
-    <row r="91" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A91" s="7" t="s">
         <v>7</v>
       </c>
@@ -16782,7 +16781,7 @@
       </c>
       <c r="H91"/>
     </row>
-    <row r="92" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A92" s="7" t="s">
         <v>7</v>
       </c>
@@ -16806,7 +16805,7 @@
       </c>
       <c r="H92"/>
     </row>
-    <row r="93" spans="1:8" ht="304" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" ht="304" x14ac:dyDescent="0.2">
       <c r="A93" s="7" t="s">
         <v>7</v>
       </c>
@@ -16830,7 +16829,7 @@
       </c>
       <c r="H93"/>
     </row>
-    <row r="94" spans="1:8" ht="350" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" ht="350" x14ac:dyDescent="0.2">
       <c r="A94" s="7" t="s">
         <v>7</v>
       </c>
@@ -16854,7 +16853,7 @@
       </c>
       <c r="H94"/>
     </row>
-    <row r="95" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A95" s="7" t="s">
         <v>7</v>
       </c>
@@ -16878,7 +16877,7 @@
       </c>
       <c r="H95"/>
     </row>
-    <row r="96" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A96" s="7" t="s">
         <v>7</v>
       </c>
@@ -16902,7 +16901,7 @@
       </c>
       <c r="H96"/>
     </row>
-    <row r="97" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A97" s="7" t="s">
         <v>7</v>
       </c>
@@ -16925,7 +16924,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:7" customFormat="1" ht="365" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" customFormat="1" ht="365" x14ac:dyDescent="0.2">
       <c r="A98" s="7" t="s">
         <v>7</v>
       </c>
@@ -16948,7 +16947,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A99" s="7" t="s">
         <v>65</v>
       </c>
@@ -16971,7 +16970,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="100" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A100" s="7" t="s">
         <v>65</v>
       </c>
@@ -16994,7 +16993,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="101" spans="1:7" customFormat="1" ht="350" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" customFormat="1" ht="350" x14ac:dyDescent="0.2">
       <c r="A101" s="7" t="s">
         <v>7</v>
       </c>
@@ -17017,7 +17016,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A102" s="7" t="s">
         <v>65</v>
       </c>
@@ -17040,7 +17039,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="103" spans="1:7" customFormat="1" ht="128" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" customFormat="1" ht="128" x14ac:dyDescent="0.2">
       <c r="A103" s="7" t="s">
         <v>7</v>
       </c>
@@ -17063,7 +17062,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:7" customFormat="1" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" customFormat="1" ht="144" x14ac:dyDescent="0.2">
       <c r="A104" s="7" t="s">
         <v>7</v>
       </c>
@@ -17086,7 +17085,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A105" s="7" t="s">
         <v>7</v>
       </c>
@@ -17109,7 +17108,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A106" s="7" t="s">
         <v>7</v>
       </c>
@@ -17132,7 +17131,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="107" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A107" s="7" t="s">
         <v>7</v>
       </c>
@@ -17155,7 +17154,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:7" customFormat="1" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" customFormat="1" ht="288" x14ac:dyDescent="0.2">
       <c r="A108" s="7" t="s">
         <v>7</v>
       </c>
@@ -17178,7 +17177,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="109" spans="1:7" customFormat="1" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" customFormat="1" ht="144" x14ac:dyDescent="0.2">
       <c r="A109" s="7" t="s">
         <v>7</v>
       </c>
@@ -17201,7 +17200,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:7" customFormat="1" ht="64" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A110" s="7" t="s">
         <v>7</v>
       </c>
@@ -17224,7 +17223,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A111" s="7" t="s">
         <v>65</v>
       </c>
@@ -17247,7 +17246,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="112" spans="1:7" customFormat="1" ht="128" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" customFormat="1" ht="128" x14ac:dyDescent="0.2">
       <c r="A112" s="7" t="s">
         <v>7</v>
       </c>
@@ -17270,7 +17269,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" ht="160" x14ac:dyDescent="0.2">
       <c r="A113" s="7" t="s">
         <v>7</v>
       </c>
@@ -17294,7 +17293,7 @@
       </c>
       <c r="H113"/>
     </row>
-    <row r="114" spans="1:8" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" ht="160" x14ac:dyDescent="0.2">
       <c r="A114" s="7" t="s">
         <v>7</v>
       </c>
@@ -17318,7 +17317,7 @@
       </c>
       <c r="H114"/>
     </row>
-    <row r="115" spans="1:8" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" ht="160" x14ac:dyDescent="0.2">
       <c r="A115" s="7" t="s">
         <v>7</v>
       </c>
@@ -17342,7 +17341,7 @@
       </c>
       <c r="H115"/>
     </row>
-    <row r="116" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A116" s="7" t="s">
         <v>7</v>
       </c>
@@ -17366,7 +17365,7 @@
       </c>
       <c r="H116"/>
     </row>
-    <row r="117" spans="1:8" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" ht="160" x14ac:dyDescent="0.2">
       <c r="A117" s="7" t="s">
         <v>7</v>
       </c>
@@ -17390,7 +17389,7 @@
       </c>
       <c r="H117"/>
     </row>
-    <row r="118" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A118" s="7" t="s">
         <v>7</v>
       </c>
@@ -17414,7 +17413,7 @@
       </c>
       <c r="H118"/>
     </row>
-    <row r="119" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A119" s="7" t="s">
         <v>7</v>
       </c>
@@ -17438,7 +17437,7 @@
       </c>
       <c r="H119"/>
     </row>
-    <row r="120" spans="1:8" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" ht="144" x14ac:dyDescent="0.2">
       <c r="A120" s="7" t="s">
         <v>7</v>
       </c>
@@ -17462,7 +17461,7 @@
       </c>
       <c r="H120"/>
     </row>
-    <row r="121" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A121" s="7" t="s">
         <v>7</v>
       </c>
@@ -17486,7 +17485,7 @@
       </c>
       <c r="H121"/>
     </row>
-    <row r="122" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A122" s="7" t="s">
         <v>7</v>
       </c>
@@ -17510,7 +17509,7 @@
       </c>
       <c r="H122"/>
     </row>
-    <row r="123" spans="1:8" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" ht="112" x14ac:dyDescent="0.2">
       <c r="A123" s="7" t="s">
         <v>7</v>
       </c>
@@ -17536,7 +17535,7 @@
         <v>2426</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A124" s="7" t="s">
         <v>7</v>
       </c>
@@ -17562,7 +17561,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A125" s="7" t="s">
         <v>7</v>
       </c>
@@ -17586,7 +17585,7 @@
       </c>
       <c r="H125"/>
     </row>
-    <row r="126" spans="1:8" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" ht="112" x14ac:dyDescent="0.2">
       <c r="A126" s="7" t="s">
         <v>7</v>
       </c>
@@ -17610,7 +17609,7 @@
       </c>
       <c r="H126"/>
     </row>
-    <row r="127" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A127" s="7" t="s">
         <v>7</v>
       </c>
@@ -17634,7 +17633,7 @@
       </c>
       <c r="H127"/>
     </row>
-    <row r="128" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A128" s="7" t="s">
         <v>7</v>
       </c>
@@ -17658,7 +17657,7 @@
       </c>
       <c r="H128"/>
     </row>
-    <row r="129" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A129" s="7" t="s">
         <v>7</v>
       </c>
@@ -17681,7 +17680,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A130" s="7" t="s">
         <v>7</v>
       </c>
@@ -17704,7 +17703,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="131" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A131" s="7" t="s">
         <v>7</v>
       </c>
@@ -17727,7 +17726,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="1:7" customFormat="1" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" customFormat="1" ht="320" x14ac:dyDescent="0.2">
       <c r="A132" s="7" t="s">
         <v>7</v>
       </c>
@@ -17750,7 +17749,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="133" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A133" s="7" t="s">
         <v>7</v>
       </c>
@@ -17773,7 +17772,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="134" spans="1:7" customFormat="1" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A134" s="7" t="s">
         <v>7</v>
       </c>
@@ -17796,7 +17795,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="135" spans="1:7" customFormat="1" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A135" s="7" t="s">
         <v>7</v>
       </c>
@@ -17819,7 +17818,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="136" spans="1:7" customFormat="1" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" customFormat="1" ht="112" x14ac:dyDescent="0.2">
       <c r="A136" s="7" t="s">
         <v>7</v>
       </c>
@@ -17842,7 +17841,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="137" spans="1:7" customFormat="1" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A137" s="7" t="s">
         <v>7</v>
       </c>
@@ -17865,7 +17864,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A138" s="7" t="s">
         <v>65</v>
       </c>
@@ -17888,7 +17887,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="139" spans="1:7" customFormat="1" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" customFormat="1" ht="144" x14ac:dyDescent="0.2">
       <c r="A139" s="7" t="s">
         <v>7</v>
       </c>
@@ -17911,7 +17910,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="140" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A140" s="7" t="s">
         <v>7</v>
       </c>
@@ -17934,7 +17933,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:7" customFormat="1" ht="350" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" customFormat="1" ht="350" x14ac:dyDescent="0.2">
       <c r="A141" s="7" t="s">
         <v>65</v>
       </c>
@@ -17957,7 +17956,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="142" spans="1:7" customFormat="1" ht="365" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" customFormat="1" ht="365" x14ac:dyDescent="0.2">
       <c r="A142" s="7" t="s">
         <v>7</v>
       </c>
@@ -17980,7 +17979,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:7" customFormat="1" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" customFormat="1" ht="288" x14ac:dyDescent="0.2">
       <c r="A143" s="7" t="s">
         <v>7</v>
       </c>
@@ -18003,7 +18002,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="144" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A144" s="7" t="s">
         <v>7</v>
       </c>
@@ -18026,7 +18025,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="145" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A145" s="7" t="s">
         <v>7</v>
       </c>
@@ -18049,7 +18048,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A146" s="7" t="s">
         <v>7</v>
       </c>
@@ -18072,7 +18071,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="147" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A147" s="7" t="s">
         <v>7</v>
       </c>
@@ -18095,7 +18094,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A148" s="7" t="s">
         <v>7</v>
       </c>
@@ -18118,7 +18117,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="149" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A149" s="7" t="s">
         <v>7</v>
       </c>
@@ -18141,7 +18140,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="150" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A150" s="7" t="s">
         <v>7</v>
       </c>
@@ -18164,7 +18163,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A151" s="7" t="s">
         <v>7</v>
       </c>
@@ -18187,7 +18186,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A152" s="7" t="s">
         <v>7</v>
       </c>
@@ -18210,7 +18209,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="153" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A153" s="7" t="s">
         <v>7</v>
       </c>
@@ -18233,7 +18232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="154" spans="1:7" customFormat="1" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A154" s="7" t="s">
         <v>7</v>
       </c>
@@ -18256,7 +18255,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A155" s="7" t="s">
         <v>7</v>
       </c>
@@ -18279,7 +18278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="156" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A156" s="7" t="s">
         <v>7</v>
       </c>
@@ -18302,7 +18301,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="157" spans="1:7" customFormat="1" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" customFormat="1" ht="112" x14ac:dyDescent="0.2">
       <c r="A157" s="7" t="s">
         <v>7</v>
       </c>
@@ -18325,7 +18324,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A158" s="7" t="s">
         <v>7</v>
       </c>
@@ -18348,7 +18347,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="159" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A159" s="7" t="s">
         <v>7</v>
       </c>
@@ -18371,7 +18370,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:7" customFormat="1" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A160" s="7" t="s">
         <v>7</v>
       </c>
@@ -18394,7 +18393,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161" spans="1:7" customFormat="1" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A161" s="7" t="s">
         <v>7</v>
       </c>
@@ -18417,7 +18416,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="162" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A162" s="7" t="s">
         <v>7</v>
       </c>
@@ -18440,7 +18439,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="163" spans="1:7" customFormat="1" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A163" s="7" t="s">
         <v>7</v>
       </c>
@@ -18463,7 +18462,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="164" spans="1:7" customFormat="1" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A164" s="7" t="s">
         <v>7</v>
       </c>
@@ -18486,7 +18485,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="165" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A165" s="7" t="s">
         <v>7</v>
       </c>
@@ -18509,7 +18508,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:7" customFormat="1" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" customFormat="1" ht="144" x14ac:dyDescent="0.2">
       <c r="A166" s="7" t="s">
         <v>7</v>
       </c>
@@ -18532,7 +18531,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="167" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A167" s="7" t="s">
         <v>7</v>
       </c>
@@ -18555,7 +18554,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:7" customFormat="1" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" customFormat="1" ht="144" x14ac:dyDescent="0.2">
       <c r="A168" s="7" t="s">
         <v>7</v>
       </c>
@@ -18578,7 +18577,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:7" customFormat="1" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" customFormat="1" ht="144" x14ac:dyDescent="0.2">
       <c r="A169" s="7" t="s">
         <v>7</v>
       </c>
@@ -18601,7 +18600,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:7" customFormat="1" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" customFormat="1" ht="144" x14ac:dyDescent="0.2">
       <c r="A170" s="7" t="s">
         <v>7</v>
       </c>
@@ -18624,7 +18623,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="171" spans="1:7" customFormat="1" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" customFormat="1" ht="144" x14ac:dyDescent="0.2">
       <c r="A171" s="7" t="s">
         <v>7</v>
       </c>
@@ -18647,7 +18646,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:7" customFormat="1" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" customFormat="1" ht="112" x14ac:dyDescent="0.2">
       <c r="A172" s="7" t="s">
         <v>7</v>
       </c>
@@ -18670,7 +18669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A173" s="7" t="s">
         <v>7</v>
       </c>
@@ -18693,7 +18692,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A174" s="7" t="s">
         <v>7</v>
       </c>
@@ -18716,7 +18715,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="175" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A175" s="7" t="s">
         <v>7</v>
       </c>
@@ -18739,7 +18738,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="176" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A176" s="7" t="s">
         <v>7</v>
       </c>
@@ -18762,7 +18761,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A177" s="7" t="s">
         <v>7</v>
       </c>
@@ -18786,7 +18785,7 @@
       </c>
       <c r="H177"/>
     </row>
-    <row r="178" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A178" s="7" t="s">
         <v>7</v>
       </c>
@@ -18810,7 +18809,7 @@
       </c>
       <c r="H178"/>
     </row>
-    <row r="179" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A179" s="7" t="s">
         <v>7</v>
       </c>
@@ -18834,7 +18833,7 @@
       </c>
       <c r="H179"/>
     </row>
-    <row r="180" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A180" s="7" t="s">
         <v>7</v>
       </c>
@@ -18858,7 +18857,7 @@
       </c>
       <c r="H180"/>
     </row>
-    <row r="181" spans="1:8" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:8" ht="256" x14ac:dyDescent="0.2">
       <c r="A181" s="7" t="s">
         <v>7</v>
       </c>
@@ -18882,7 +18881,7 @@
       </c>
       <c r="H181"/>
     </row>
-    <row r="182" spans="1:8" ht="64" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A182" s="7" t="s">
         <v>7</v>
       </c>
@@ -18906,7 +18905,7 @@
       </c>
       <c r="H182"/>
     </row>
-    <row r="183" spans="1:8" ht="80" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A183" s="7" t="s">
         <v>7</v>
       </c>
@@ -18930,7 +18929,7 @@
       </c>
       <c r="H183"/>
     </row>
-    <row r="184" spans="1:8" ht="80" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A184" s="7" t="s">
         <v>7</v>
       </c>
@@ -18954,7 +18953,7 @@
       </c>
       <c r="H184"/>
     </row>
-    <row r="185" spans="1:8" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A185" s="7" t="s">
         <v>7</v>
       </c>
@@ -18978,7 +18977,7 @@
       </c>
       <c r="H185"/>
     </row>
-    <row r="186" spans="1:8" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:8" ht="112" x14ac:dyDescent="0.2">
       <c r="A186" s="7" t="s">
         <v>7</v>
       </c>
@@ -19002,7 +19001,7 @@
       </c>
       <c r="H186"/>
     </row>
-    <row r="187" spans="1:8" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A187" s="7" t="s">
         <v>7</v>
       </c>
@@ -19026,7 +19025,7 @@
       </c>
       <c r="H187"/>
     </row>
-    <row r="188" spans="1:8" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A188" s="7" t="s">
         <v>7</v>
       </c>
@@ -19050,7 +19049,7 @@
       </c>
       <c r="H188"/>
     </row>
-    <row r="189" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A189" s="7" t="s">
         <v>440</v>
       </c>
@@ -19074,7 +19073,7 @@
       </c>
       <c r="H189"/>
     </row>
-    <row r="190" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A190" s="7" t="s">
         <v>440</v>
       </c>
@@ -19100,7 +19099,7 @@
         <v>2506</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A191" s="7" t="s">
         <v>440</v>
       </c>
@@ -19126,7 +19125,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:8" ht="288" x14ac:dyDescent="0.2">
       <c r="A192" s="7" t="s">
         <v>440</v>
       </c>
@@ -19150,7 +19149,7 @@
       </c>
       <c r="H192"/>
     </row>
-    <row r="193" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A193" s="7" t="s">
         <v>440</v>
       </c>
@@ -19173,7 +19172,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="194" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A194" s="7" t="s">
         <v>440</v>
       </c>
@@ -19196,7 +19195,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="195" spans="1:7" customFormat="1" ht="395" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" customFormat="1" ht="395" x14ac:dyDescent="0.2">
       <c r="A195" s="7" t="s">
         <v>65</v>
       </c>
@@ -19219,7 +19218,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="196" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A196" s="7" t="s">
         <v>440</v>
       </c>
@@ -19242,7 +19241,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="197" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A197" s="7" t="s">
         <v>440</v>
       </c>
@@ -19265,7 +19264,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="198" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A198" s="7" t="s">
         <v>440</v>
       </c>
@@ -19288,7 +19287,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="199" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A199" s="7" t="s">
         <v>440</v>
       </c>
@@ -19311,7 +19310,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="200" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A200" s="7" t="s">
         <v>440</v>
       </c>
@@ -19334,7 +19333,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="201" spans="1:7" customFormat="1" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" customFormat="1" ht="288" x14ac:dyDescent="0.2">
       <c r="A201" s="7" t="s">
         <v>440</v>
       </c>
@@ -19357,7 +19356,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="202" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A202" s="7" t="s">
         <v>440</v>
       </c>
@@ -19380,7 +19379,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="203" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A203" s="7" t="s">
         <v>440</v>
       </c>
@@ -19403,7 +19402,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="204" spans="1:7" customFormat="1" ht="395" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" customFormat="1" ht="395" x14ac:dyDescent="0.2">
       <c r="A204" s="7" t="s">
         <v>440</v>
       </c>
@@ -19426,7 +19425,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="205" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A205" s="7" t="s">
         <v>440</v>
       </c>
@@ -19449,7 +19448,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="206" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A206" s="7" t="s">
         <v>440</v>
       </c>
@@ -19472,7 +19471,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="207" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A207" s="7" t="s">
         <v>440</v>
       </c>
@@ -19495,7 +19494,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="208" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A208" s="7" t="s">
         <v>440</v>
       </c>
@@ -19518,7 +19517,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A209" s="7" t="s">
         <v>440</v>
       </c>
@@ -19542,7 +19541,7 @@
       </c>
       <c r="H209"/>
     </row>
-    <row r="210" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A210" s="7" t="s">
         <v>440</v>
       </c>
@@ -19566,7 +19565,7 @@
       </c>
       <c r="H210"/>
     </row>
-    <row r="211" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A211" s="7" t="s">
         <v>440</v>
       </c>
@@ -19590,7 +19589,7 @@
       </c>
       <c r="H211"/>
     </row>
-    <row r="212" spans="1:8" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:8" ht="320" x14ac:dyDescent="0.2">
       <c r="A212" s="7" t="s">
         <v>440</v>
       </c>
@@ -19614,7 +19613,7 @@
       </c>
       <c r="H212"/>
     </row>
-    <row r="213" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A213" s="7" t="s">
         <v>440</v>
       </c>
@@ -19638,7 +19637,7 @@
       </c>
       <c r="H213"/>
     </row>
-    <row r="214" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A214" s="7" t="s">
         <v>440</v>
       </c>
@@ -19662,7 +19661,7 @@
       </c>
       <c r="H214"/>
     </row>
-    <row r="215" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A215" s="7" t="s">
         <v>440</v>
       </c>
@@ -19686,7 +19685,7 @@
       </c>
       <c r="H215"/>
     </row>
-    <row r="216" spans="1:8" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:8" ht="256" x14ac:dyDescent="0.2">
       <c r="A216" s="7" t="s">
         <v>440</v>
       </c>
@@ -19710,7 +19709,7 @@
       </c>
       <c r="H216"/>
     </row>
-    <row r="217" spans="1:8" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:8" ht="240" x14ac:dyDescent="0.2">
       <c r="A217" s="7" t="s">
         <v>440</v>
       </c>
@@ -19734,7 +19733,7 @@
       </c>
       <c r="H217"/>
     </row>
-    <row r="218" spans="1:8" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:8" ht="272" x14ac:dyDescent="0.2">
       <c r="A218" s="7" t="s">
         <v>440</v>
       </c>
@@ -19758,7 +19757,7 @@
       </c>
       <c r="H218"/>
     </row>
-    <row r="219" spans="1:8" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:8" ht="256" x14ac:dyDescent="0.2">
       <c r="A219" s="7" t="s">
         <v>440</v>
       </c>
@@ -19782,7 +19781,7 @@
       </c>
       <c r="H219"/>
     </row>
-    <row r="220" spans="1:8" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:8" ht="256" x14ac:dyDescent="0.2">
       <c r="A220" s="7" t="s">
         <v>440</v>
       </c>
@@ -19806,7 +19805,7 @@
       </c>
       <c r="H220"/>
     </row>
-    <row r="221" spans="1:8" ht="380" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:8" ht="380" x14ac:dyDescent="0.2">
       <c r="A221" s="7" t="s">
         <v>440</v>
       </c>
@@ -19832,7 +19831,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A222" s="7" t="s">
         <v>440</v>
       </c>
@@ -19856,7 +19855,7 @@
       </c>
       <c r="H222"/>
     </row>
-    <row r="223" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A223" s="7" t="s">
         <v>440</v>
       </c>
@@ -19880,7 +19879,7 @@
       </c>
       <c r="H223"/>
     </row>
-    <row r="224" spans="1:8" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:8" ht="288" x14ac:dyDescent="0.2">
       <c r="A224" s="7" t="s">
         <v>440</v>
       </c>
@@ -19906,7 +19905,7 @@
         <v>2483</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:8" ht="288" x14ac:dyDescent="0.2">
       <c r="A225" s="7" t="s">
         <v>440</v>
       </c>
@@ -19932,7 +19931,7 @@
         <v>2482</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="365" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:8" ht="365" x14ac:dyDescent="0.2">
       <c r="A226" s="7" t="s">
         <v>440</v>
       </c>
@@ -19956,7 +19955,7 @@
       </c>
       <c r="H226"/>
     </row>
-    <row r="227" spans="1:8" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:8" ht="288" x14ac:dyDescent="0.2">
       <c r="A227" s="7" t="s">
         <v>440</v>
       </c>
@@ -19980,7 +19979,7 @@
       </c>
       <c r="H227"/>
     </row>
-    <row r="228" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A228" s="7" t="s">
         <v>440</v>
       </c>
@@ -20004,7 +20003,7 @@
       </c>
       <c r="H228"/>
     </row>
-    <row r="229" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A229" s="7" t="s">
         <v>440</v>
       </c>
@@ -20028,7 +20027,7 @@
       </c>
       <c r="H229"/>
     </row>
-    <row r="230" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A230" s="7" t="s">
         <v>440</v>
       </c>
@@ -20052,7 +20051,7 @@
       </c>
       <c r="H230"/>
     </row>
-    <row r="231" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A231" s="7" t="s">
         <v>440</v>
       </c>
@@ -20076,7 +20075,7 @@
       </c>
       <c r="H231"/>
     </row>
-    <row r="232" spans="1:8" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:8" ht="288" x14ac:dyDescent="0.2">
       <c r="A232" s="7" t="s">
         <v>440</v>
       </c>
@@ -20102,7 +20101,7 @@
         <v>2475</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="304" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:8" ht="304" x14ac:dyDescent="0.2">
       <c r="A233" s="7" t="s">
         <v>440</v>
       </c>
@@ -20128,7 +20127,7 @@
         <v>2475</v>
       </c>
     </row>
-    <row r="234" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A234" s="7" t="s">
         <v>440</v>
       </c>
@@ -20154,7 +20153,7 @@
         <v>2476</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:8" ht="335" x14ac:dyDescent="0.2">
       <c r="A235" s="7" t="s">
         <v>440</v>
       </c>
@@ -20178,7 +20177,7 @@
       </c>
       <c r="H235"/>
     </row>
-    <row r="236" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A236" s="7" t="s">
         <v>440</v>
       </c>
@@ -20202,7 +20201,7 @@
       </c>
       <c r="H236"/>
     </row>
-    <row r="237" spans="1:8" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A237" s="7" t="s">
         <v>440</v>
       </c>
@@ -20226,7 +20225,7 @@
       </c>
       <c r="H237"/>
     </row>
-    <row r="238" spans="1:8" ht="128" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:8" ht="128" x14ac:dyDescent="0.2">
       <c r="A238" s="7" t="s">
         <v>440</v>
       </c>
@@ -20252,7 +20251,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:8" ht="144" x14ac:dyDescent="0.2">
       <c r="A239" s="7" t="s">
         <v>440</v>
       </c>
@@ -20276,7 +20275,7 @@
       </c>
       <c r="H239"/>
     </row>
-    <row r="240" spans="1:8" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:8" ht="144" x14ac:dyDescent="0.2">
       <c r="A240" s="7" t="s">
         <v>440</v>
       </c>
@@ -20302,7 +20301,7 @@
         <v>2515</v>
       </c>
     </row>
-    <row r="241" spans="1:8" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:8" ht="144" x14ac:dyDescent="0.2">
       <c r="A241" s="7" t="s">
         <v>440</v>
       </c>
@@ -20326,7 +20325,7 @@
       </c>
       <c r="H241"/>
     </row>
-    <row r="242" spans="1:8" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:8" ht="144" x14ac:dyDescent="0.2">
       <c r="A242" s="7" t="s">
         <v>440</v>
       </c>
@@ -20350,7 +20349,7 @@
       </c>
       <c r="H242"/>
     </row>
-    <row r="243" spans="1:8" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A243" s="7" t="s">
         <v>65</v>
       </c>
@@ -20376,7 +20375,7 @@
         <v>2647</v>
       </c>
     </row>
-    <row r="244" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A244" s="7" t="s">
         <v>440</v>
       </c>
@@ -20400,7 +20399,7 @@
       </c>
       <c r="H244"/>
     </row>
-    <row r="245" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A245" s="7" t="s">
         <v>440</v>
       </c>
@@ -20424,7 +20423,7 @@
       </c>
       <c r="H245"/>
     </row>
-    <row r="246" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A246" s="7" t="s">
         <v>440</v>
       </c>
@@ -20448,7 +20447,7 @@
       </c>
       <c r="H246"/>
     </row>
-    <row r="247" spans="1:8" ht="128" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:8" ht="128" x14ac:dyDescent="0.2">
       <c r="A247" s="7" t="s">
         <v>440</v>
       </c>
@@ -20474,7 +20473,7 @@
         <v>2528</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A248" s="7" t="s">
         <v>440</v>
       </c>
@@ -20498,7 +20497,7 @@
       </c>
       <c r="H248"/>
     </row>
-    <row r="249" spans="1:8" ht="380" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:8" ht="380" x14ac:dyDescent="0.2">
       <c r="A249" s="7" t="s">
         <v>440</v>
       </c>
@@ -20522,7 +20521,7 @@
       </c>
       <c r="H249"/>
     </row>
-    <row r="250" spans="1:8" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A250" s="7" t="s">
         <v>440</v>
       </c>
@@ -20546,7 +20545,7 @@
       </c>
       <c r="H250"/>
     </row>
-    <row r="251" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A251" s="7" t="s">
         <v>440</v>
       </c>
@@ -20570,7 +20569,7 @@
       </c>
       <c r="H251"/>
     </row>
-    <row r="252" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A252" s="7" t="s">
         <v>440</v>
       </c>
@@ -20594,7 +20593,7 @@
       </c>
       <c r="H252"/>
     </row>
-    <row r="253" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A253" s="7" t="s">
         <v>440</v>
       </c>
@@ -20618,7 +20617,7 @@
       </c>
       <c r="H253"/>
     </row>
-    <row r="254" spans="1:8" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:8" ht="256" x14ac:dyDescent="0.2">
       <c r="A254" s="7" t="s">
         <v>440</v>
       </c>
@@ -20642,7 +20641,7 @@
       </c>
       <c r="H254"/>
     </row>
-    <row r="255" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A255" s="7" t="s">
         <v>440</v>
       </c>
@@ -20666,7 +20665,7 @@
       </c>
       <c r="H255"/>
     </row>
-    <row r="256" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A256" s="7" t="s">
         <v>440</v>
       </c>
@@ -20690,7 +20689,7 @@
       </c>
       <c r="H256"/>
     </row>
-    <row r="257" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A257" s="7" t="s">
         <v>440</v>
       </c>
@@ -20713,7 +20712,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="258" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A258" s="7" t="s">
         <v>440</v>
       </c>
@@ -20736,7 +20735,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="259" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A259" s="7" t="s">
         <v>440</v>
       </c>
@@ -20759,7 +20758,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="260" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A260" s="7" t="s">
         <v>440</v>
       </c>
@@ -20782,7 +20781,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="261" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A261" s="7" t="s">
         <v>440</v>
       </c>
@@ -20805,7 +20804,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="262" spans="1:7" customFormat="1" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7" customFormat="1" ht="320" x14ac:dyDescent="0.2">
       <c r="A262" s="7" t="s">
         <v>440</v>
       </c>
@@ -20828,7 +20827,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="263" spans="1:7" customFormat="1" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7" customFormat="1" ht="320" x14ac:dyDescent="0.2">
       <c r="A263" s="7" t="s">
         <v>440</v>
       </c>
@@ -20851,7 +20850,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="264" spans="1:7" customFormat="1" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7" customFormat="1" ht="320" x14ac:dyDescent="0.2">
       <c r="A264" s="7" t="s">
         <v>440</v>
       </c>
@@ -20874,7 +20873,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="265" spans="1:7" customFormat="1" ht="304" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:7" customFormat="1" ht="304" x14ac:dyDescent="0.2">
       <c r="A265" s="7" t="s">
         <v>440</v>
       </c>
@@ -20897,7 +20896,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="266" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A266" s="7" t="s">
         <v>440</v>
       </c>
@@ -20920,7 +20919,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="267" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A267" s="7" t="s">
         <v>440</v>
       </c>
@@ -20943,7 +20942,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="268" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A268" s="7" t="s">
         <v>440</v>
       </c>
@@ -20966,7 +20965,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="269" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A269" s="7" t="s">
         <v>440</v>
       </c>
@@ -20989,7 +20988,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="270" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A270" s="7" t="s">
         <v>440</v>
       </c>
@@ -21012,7 +21011,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="271" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A271" s="7" t="s">
         <v>440</v>
       </c>
@@ -21035,7 +21034,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="272" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A272" s="7" t="s">
         <v>440</v>
       </c>
@@ -21058,7 +21057,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="273" spans="1:8" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:8" ht="256" x14ac:dyDescent="0.2">
       <c r="A273" s="7" t="s">
         <v>440</v>
       </c>
@@ -21082,7 +21081,7 @@
       </c>
       <c r="H273"/>
     </row>
-    <row r="274" spans="1:8" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:8" ht="272" x14ac:dyDescent="0.2">
       <c r="A274" s="7" t="s">
         <v>440</v>
       </c>
@@ -21106,7 +21105,7 @@
       </c>
       <c r="H274"/>
     </row>
-    <row r="275" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A275" s="7" t="s">
         <v>440</v>
       </c>
@@ -21132,7 +21131,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="276" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A276" s="7" t="s">
         <v>440</v>
       </c>
@@ -21158,7 +21157,7 @@
         <v>2470</v>
       </c>
     </row>
-    <row r="277" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A277" s="7" t="s">
         <v>440</v>
       </c>
@@ -21184,7 +21183,7 @@
         <v>2471</v>
       </c>
     </row>
-    <row r="278" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A278" s="7" t="s">
         <v>440</v>
       </c>
@@ -21208,7 +21207,7 @@
       </c>
       <c r="H278"/>
     </row>
-    <row r="279" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A279" s="7" t="s">
         <v>440</v>
       </c>
@@ -21232,7 +21231,7 @@
       </c>
       <c r="H279"/>
     </row>
-    <row r="280" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A280" s="7" t="s">
         <v>440</v>
       </c>
@@ -21256,7 +21255,7 @@
       </c>
       <c r="H280"/>
     </row>
-    <row r="281" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A281" s="7" t="s">
         <v>440</v>
       </c>
@@ -21282,7 +21281,7 @@
         <v>2455</v>
       </c>
     </row>
-    <row r="282" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A282" s="7" t="s">
         <v>440</v>
       </c>
@@ -21308,7 +21307,7 @@
         <v>2460</v>
       </c>
     </row>
-    <row r="283" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A283" s="7" t="s">
         <v>440</v>
       </c>
@@ -21334,7 +21333,7 @@
         <v>2461</v>
       </c>
     </row>
-    <row r="284" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A284" s="7" t="s">
         <v>440</v>
       </c>
@@ -21360,7 +21359,7 @@
         <v>2462</v>
       </c>
     </row>
-    <row r="285" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A285" s="7" t="s">
         <v>440</v>
       </c>
@@ -21386,7 +21385,7 @@
         <v>2464</v>
       </c>
     </row>
-    <row r="286" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A286" s="7" t="s">
         <v>440</v>
       </c>
@@ -21412,7 +21411,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="287" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A287" s="7" t="s">
         <v>440</v>
       </c>
@@ -21438,7 +21437,7 @@
         <v>2465</v>
       </c>
     </row>
-    <row r="288" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A288" s="7" t="s">
         <v>440</v>
       </c>
@@ -21464,7 +21463,7 @@
         <v>2459</v>
       </c>
     </row>
-    <row r="289" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A289" s="7" t="s">
         <v>440</v>
       </c>
@@ -21490,7 +21489,7 @@
         <v>2457</v>
       </c>
     </row>
-    <row r="290" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A290" s="7" t="s">
         <v>440</v>
       </c>
@@ -21516,7 +21515,7 @@
         <v>2458</v>
       </c>
     </row>
-    <row r="291" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A291" s="7" t="s">
         <v>440</v>
       </c>
@@ -21540,7 +21539,7 @@
       </c>
       <c r="H291"/>
     </row>
-    <row r="292" spans="1:8" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:8" ht="256" x14ac:dyDescent="0.2">
       <c r="A292" s="7" t="s">
         <v>440</v>
       </c>
@@ -21564,7 +21563,7 @@
       </c>
       <c r="H292"/>
     </row>
-    <row r="293" spans="1:8" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:8" ht="144" x14ac:dyDescent="0.2">
       <c r="A293" s="7" t="s">
         <v>440</v>
       </c>
@@ -21588,7 +21587,7 @@
       </c>
       <c r="H293"/>
     </row>
-    <row r="294" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A294" s="7" t="s">
         <v>440</v>
       </c>
@@ -21612,7 +21611,7 @@
       </c>
       <c r="H294"/>
     </row>
-    <row r="295" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A295" s="7" t="s">
         <v>440</v>
       </c>
@@ -21636,7 +21635,7 @@
       </c>
       <c r="H295"/>
     </row>
-    <row r="296" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A296" s="7" t="s">
         <v>440</v>
       </c>
@@ -21660,7 +21659,7 @@
       </c>
       <c r="H296"/>
     </row>
-    <row r="297" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A297" s="7" t="s">
         <v>440</v>
       </c>
@@ -21684,7 +21683,7 @@
       </c>
       <c r="H297"/>
     </row>
-    <row r="298" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A298" s="7" t="s">
         <v>440</v>
       </c>
@@ -21708,7 +21707,7 @@
       </c>
       <c r="H298"/>
     </row>
-    <row r="299" spans="1:8" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:8" ht="320" x14ac:dyDescent="0.2">
       <c r="A299" s="7" t="s">
         <v>440</v>
       </c>
@@ -21732,7 +21731,7 @@
       </c>
       <c r="H299"/>
     </row>
-    <row r="300" spans="1:8" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:8" ht="256" x14ac:dyDescent="0.2">
       <c r="A300" s="7" t="s">
         <v>440</v>
       </c>
@@ -21756,7 +21755,7 @@
       </c>
       <c r="H300"/>
     </row>
-    <row r="301" spans="1:8" ht="350" hidden="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:8" ht="350" x14ac:dyDescent="0.2">
       <c r="A301" s="7" t="s">
         <v>440</v>
       </c>
@@ -21780,7 +21779,7 @@
       </c>
       <c r="H301"/>
     </row>
-    <row r="302" spans="1:8" ht="365" hidden="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:8" ht="365" x14ac:dyDescent="0.2">
       <c r="A302" s="7" t="s">
         <v>440</v>
       </c>
@@ -21804,7 +21803,7 @@
       </c>
       <c r="H302"/>
     </row>
-    <row r="303" spans="1:8" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:8" ht="160" x14ac:dyDescent="0.2">
       <c r="A303" s="7" t="s">
         <v>440</v>
       </c>
@@ -21828,7 +21827,7 @@
       </c>
       <c r="H303"/>
     </row>
-    <row r="304" spans="1:8" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:8" ht="160" x14ac:dyDescent="0.2">
       <c r="A304" s="7" t="s">
         <v>440</v>
       </c>
@@ -21852,7 +21851,7 @@
       </c>
       <c r="H304"/>
     </row>
-    <row r="305" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A305" s="7" t="s">
         <v>440</v>
       </c>
@@ -21875,7 +21874,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="306" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A306" s="7" t="s">
         <v>440</v>
       </c>
@@ -21898,7 +21897,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="307" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A307" s="7" t="s">
         <v>440</v>
       </c>
@@ -21921,7 +21920,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="308" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A308" s="7" t="s">
         <v>440</v>
       </c>
@@ -21944,7 +21943,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="309" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A309" s="7" t="s">
         <v>440</v>
       </c>
@@ -21967,7 +21966,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="310" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A310" s="7" t="s">
         <v>440</v>
       </c>
@@ -21990,7 +21989,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="311" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A311" s="7" t="s">
         <v>440</v>
       </c>
@@ -22013,7 +22012,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="312" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A312" s="7" t="s">
         <v>440</v>
       </c>
@@ -22036,7 +22035,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="313" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A313" s="7" t="s">
         <v>440</v>
       </c>
@@ -22059,7 +22058,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="314" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A314" s="7" t="s">
         <v>440</v>
       </c>
@@ -22082,7 +22081,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="315" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A315" s="7" t="s">
         <v>440</v>
       </c>
@@ -22105,7 +22104,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="316" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A316" s="7" t="s">
         <v>440</v>
       </c>
@@ -22128,7 +22127,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="317" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A317" s="7" t="s">
         <v>440</v>
       </c>
@@ -22151,7 +22150,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="318" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A318" s="7" t="s">
         <v>440</v>
       </c>
@@ -22174,7 +22173,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="319" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A319" s="7" t="s">
         <v>440</v>
       </c>
@@ -22197,7 +22196,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="320" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A320" s="7" t="s">
         <v>440</v>
       </c>
@@ -22220,7 +22219,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="321" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A321" s="7" t="s">
         <v>440</v>
       </c>
@@ -22243,7 +22242,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="322" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A322" s="7" t="s">
         <v>440</v>
       </c>
@@ -22266,7 +22265,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="323" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A323" s="7" t="s">
         <v>440</v>
       </c>
@@ -22289,7 +22288,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="324" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A324" s="7" t="s">
         <v>440</v>
       </c>
@@ -22312,7 +22311,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="325" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A325" s="7" t="s">
         <v>440</v>
       </c>
@@ -22335,7 +22334,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="326" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A326" s="7" t="s">
         <v>440</v>
       </c>
@@ -22358,7 +22357,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="327" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A327" s="7" t="s">
         <v>440</v>
       </c>
@@ -22381,7 +22380,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="328" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A328" s="7" t="s">
         <v>440</v>
       </c>
@@ -22404,7 +22403,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="329" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A329" s="7" t="s">
         <v>440</v>
       </c>
@@ -22427,7 +22426,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="330" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A330" s="7" t="s">
         <v>440</v>
       </c>
@@ -22450,7 +22449,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="331" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A331" s="7" t="s">
         <v>440</v>
       </c>
@@ -22473,7 +22472,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="332" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A332" s="7" t="s">
         <v>440</v>
       </c>
@@ -22496,7 +22495,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="333" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A333" s="7" t="s">
         <v>440</v>
       </c>
@@ -22519,7 +22518,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="334" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A334" s="7" t="s">
         <v>440</v>
       </c>
@@ -22542,7 +22541,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="335" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A335" s="7" t="s">
         <v>440</v>
       </c>
@@ -22565,7 +22564,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="336" spans="1:7" customFormat="1" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:7" customFormat="1" ht="288" x14ac:dyDescent="0.2">
       <c r="A336" s="7" t="s">
         <v>440</v>
       </c>
@@ -22588,7 +22587,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="337" spans="1:7" customFormat="1" ht="304" hidden="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:7" customFormat="1" ht="304" x14ac:dyDescent="0.2">
       <c r="A337" s="7" t="s">
         <v>440</v>
       </c>
@@ -22611,7 +22610,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="338" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A338" s="7" t="s">
         <v>440</v>
       </c>
@@ -22634,7 +22633,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="339" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A339" s="7" t="s">
         <v>440</v>
       </c>
@@ -22657,7 +22656,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="340" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A340" s="7" t="s">
         <v>440</v>
       </c>
@@ -22680,7 +22679,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="341" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A341" s="7" t="s">
         <v>440</v>
       </c>
@@ -22703,7 +22702,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="342" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A342" s="7" t="s">
         <v>440</v>
       </c>
@@ -22726,7 +22725,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="343" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A343" s="7" t="s">
         <v>440</v>
       </c>
@@ -22749,7 +22748,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="344" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A344" s="7" t="s">
         <v>440</v>
       </c>
@@ -22772,7 +22771,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="345" spans="1:7" customFormat="1" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:7" customFormat="1" ht="144" x14ac:dyDescent="0.2">
       <c r="A345" s="7" t="s">
         <v>440</v>
       </c>
@@ -22795,7 +22794,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="346" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A346" s="7" t="s">
         <v>440</v>
       </c>
@@ -22818,7 +22817,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="347" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A347" s="7" t="s">
         <v>65</v>
       </c>
@@ -22841,7 +22840,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="348" spans="1:7" customFormat="1" ht="395" hidden="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:7" customFormat="1" ht="395" x14ac:dyDescent="0.2">
       <c r="A348" s="7" t="s">
         <v>65</v>
       </c>
@@ -22864,7 +22863,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="349" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A349" s="7" t="s">
         <v>440</v>
       </c>
@@ -22887,7 +22886,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="350" spans="1:7" customFormat="1" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:7" customFormat="1" ht="335" x14ac:dyDescent="0.2">
       <c r="A350" s="7" t="s">
         <v>440</v>
       </c>
@@ -22910,7 +22909,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="351" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A351" s="7" t="s">
         <v>440</v>
       </c>
@@ -22933,7 +22932,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="352" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A352" s="7" t="s">
         <v>440</v>
       </c>
@@ -22956,7 +22955,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="353" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A353" s="7" t="s">
         <v>440</v>
       </c>
@@ -22980,7 +22979,7 @@
       </c>
       <c r="H353"/>
     </row>
-    <row r="354" spans="1:8" ht="380" hidden="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:8" ht="380" x14ac:dyDescent="0.2">
       <c r="A354" s="7" t="s">
         <v>440</v>
       </c>
@@ -23004,7 +23003,7 @@
       </c>
       <c r="H354"/>
     </row>
-    <row r="355" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A355" s="7" t="s">
         <v>440</v>
       </c>
@@ -23030,7 +23029,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="356" spans="1:8" ht="395" hidden="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:8" ht="395" x14ac:dyDescent="0.2">
       <c r="A356" s="7" t="s">
         <v>65</v>
       </c>
@@ -23056,7 +23055,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="357" spans="1:8" ht="395" hidden="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:8" ht="395" x14ac:dyDescent="0.2">
       <c r="A357" s="7" t="s">
         <v>440</v>
       </c>
@@ -23080,7 +23079,7 @@
       </c>
       <c r="H357"/>
     </row>
-    <row r="358" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A358" s="7" t="s">
         <v>440</v>
       </c>
@@ -23104,7 +23103,7 @@
       </c>
       <c r="H358"/>
     </row>
-    <row r="359" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A359" s="7" t="s">
         <v>440</v>
       </c>
@@ -23128,7 +23127,7 @@
       </c>
       <c r="H359"/>
     </row>
-    <row r="360" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A360" s="7" t="s">
         <v>440</v>
       </c>
@@ -23152,7 +23151,7 @@
       </c>
       <c r="H360"/>
     </row>
-    <row r="361" spans="1:8" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:8" ht="240" x14ac:dyDescent="0.2">
       <c r="A361" s="7" t="s">
         <v>440</v>
       </c>
@@ -23176,7 +23175,7 @@
       </c>
       <c r="H361"/>
     </row>
-    <row r="362" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A362" s="7" t="s">
         <v>440</v>
       </c>
@@ -23200,7 +23199,7 @@
       </c>
       <c r="H362"/>
     </row>
-    <row r="363" spans="1:8" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:8" ht="272" x14ac:dyDescent="0.2">
       <c r="A363" s="7" t="s">
         <v>440</v>
       </c>
@@ -23224,7 +23223,7 @@
       </c>
       <c r="H363"/>
     </row>
-    <row r="364" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A364" s="7" t="s">
         <v>440</v>
       </c>
@@ -23248,7 +23247,7 @@
       </c>
       <c r="H364"/>
     </row>
-    <row r="365" spans="1:8" ht="304" hidden="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:8" ht="304" x14ac:dyDescent="0.2">
       <c r="A365" s="7" t="s">
         <v>440</v>
       </c>
@@ -23272,7 +23271,7 @@
       </c>
       <c r="H365"/>
     </row>
-    <row r="366" spans="1:8" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:8" ht="240" x14ac:dyDescent="0.2">
       <c r="A366" s="7" t="s">
         <v>440</v>
       </c>
@@ -23296,7 +23295,7 @@
       </c>
       <c r="H366"/>
     </row>
-    <row r="367" spans="1:8" ht="128" hidden="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:8" ht="128" x14ac:dyDescent="0.2">
       <c r="A367" s="7" t="s">
         <v>440</v>
       </c>
@@ -23320,7 +23319,7 @@
       </c>
       <c r="H367"/>
     </row>
-    <row r="368" spans="1:8" ht="112" hidden="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:8" ht="112" x14ac:dyDescent="0.2">
       <c r="A368" s="7" t="s">
         <v>440</v>
       </c>
@@ -23344,7 +23343,7 @@
       </c>
       <c r="H368"/>
     </row>
-    <row r="369" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A369" s="7" t="s">
         <v>440</v>
       </c>
@@ -23368,7 +23367,7 @@
       </c>
       <c r="H369"/>
     </row>
-    <row r="370" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A370" s="7" t="s">
         <v>440</v>
       </c>
@@ -23468,7 +23467,7 @@
       </c>
       <c r="H373"/>
     </row>
-    <row r="374" spans="1:8" ht="395" hidden="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:8" ht="395" x14ac:dyDescent="0.2">
       <c r="A374" s="7" t="s">
         <v>440</v>
       </c>
@@ -23492,7 +23491,7 @@
       </c>
       <c r="H374"/>
     </row>
-    <row r="375" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A375" s="7" t="s">
         <v>440</v>
       </c>
@@ -23540,7 +23539,7 @@
       </c>
       <c r="H376"/>
     </row>
-    <row r="377" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A377" s="7" t="s">
         <v>440</v>
       </c>
@@ -23564,7 +23563,7 @@
       </c>
       <c r="H377"/>
     </row>
-    <row r="378" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A378" s="7" t="s">
         <v>440</v>
       </c>
@@ -23588,7 +23587,7 @@
       </c>
       <c r="H378"/>
     </row>
-    <row r="379" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A379" s="7" t="s">
         <v>440</v>
       </c>
@@ -23612,7 +23611,7 @@
       </c>
       <c r="H379"/>
     </row>
-    <row r="380" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A380" s="7" t="s">
         <v>440</v>
       </c>
@@ -23636,7 +23635,7 @@
       </c>
       <c r="H380"/>
     </row>
-    <row r="381" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A381" s="7" t="s">
         <v>440</v>
       </c>
@@ -23684,7 +23683,7 @@
       </c>
       <c r="H382"/>
     </row>
-    <row r="383" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A383" s="7" t="s">
         <v>440</v>
       </c>
@@ -23710,7 +23709,7 @@
         <v>2542</v>
       </c>
     </row>
-    <row r="384" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A384" s="7" t="s">
         <v>440</v>
       </c>
@@ -23734,7 +23733,7 @@
       </c>
       <c r="H384"/>
     </row>
-    <row r="385" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A385" s="7" t="s">
         <v>440</v>
       </c>
@@ -23758,7 +23757,7 @@
       </c>
       <c r="H385"/>
     </row>
-    <row r="386" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A386" s="7" t="s">
         <v>440</v>
       </c>
@@ -23782,7 +23781,7 @@
       </c>
       <c r="H386"/>
     </row>
-    <row r="387" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A387" s="7" t="s">
         <v>440</v>
       </c>
@@ -23806,7 +23805,7 @@
       </c>
       <c r="H387"/>
     </row>
-    <row r="388" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A388" s="7" t="s">
         <v>440</v>
       </c>
@@ -23830,7 +23829,7 @@
       </c>
       <c r="H388"/>
     </row>
-    <row r="389" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A389" s="7" t="s">
         <v>440</v>
       </c>
@@ -23854,7 +23853,7 @@
       </c>
       <c r="H389"/>
     </row>
-    <row r="390" spans="1:8" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A390" s="7" t="s">
         <v>440</v>
       </c>
@@ -23878,7 +23877,7 @@
       </c>
       <c r="H390"/>
     </row>
-    <row r="391" spans="1:8" ht="380" hidden="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:8" ht="380" x14ac:dyDescent="0.2">
       <c r="A391" s="7" t="s">
         <v>65</v>
       </c>
@@ -23902,7 +23901,7 @@
       </c>
       <c r="H391"/>
     </row>
-    <row r="392" spans="1:8" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A392" s="7" t="s">
         <v>440</v>
       </c>
@@ -23926,7 +23925,7 @@
       </c>
       <c r="H392"/>
     </row>
-    <row r="393" spans="1:8" ht="365" hidden="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:8" ht="365" x14ac:dyDescent="0.2">
       <c r="A393" s="7" t="s">
         <v>440</v>
       </c>
@@ -23952,7 +23951,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="394" spans="1:8" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:8" ht="256" x14ac:dyDescent="0.2">
       <c r="A394" s="7" t="s">
         <v>440</v>
       </c>
@@ -23976,7 +23975,7 @@
       </c>
       <c r="H394"/>
     </row>
-    <row r="395" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A395" s="7" t="s">
         <v>440</v>
       </c>
@@ -24000,7 +23999,7 @@
       </c>
       <c r="H395"/>
     </row>
-    <row r="396" spans="1:8" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A396" s="7" t="s">
         <v>440</v>
       </c>
@@ -24024,7 +24023,7 @@
       </c>
       <c r="H396"/>
     </row>
-    <row r="397" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A397" s="7" t="s">
         <v>440</v>
       </c>
@@ -24048,7 +24047,7 @@
       </c>
       <c r="H397"/>
     </row>
-    <row r="398" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A398" s="7" t="s">
         <v>440</v>
       </c>
@@ -24072,7 +24071,7 @@
       </c>
       <c r="H398"/>
     </row>
-    <row r="399" spans="1:8" ht="350" hidden="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:8" ht="350" x14ac:dyDescent="0.2">
       <c r="A399" s="7" t="s">
         <v>440</v>
       </c>
@@ -24096,7 +24095,7 @@
       </c>
       <c r="H399"/>
     </row>
-    <row r="400" spans="1:8" ht="365" hidden="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:8" ht="365" x14ac:dyDescent="0.2">
       <c r="A400" s="7" t="s">
         <v>440</v>
       </c>
@@ -24120,7 +24119,7 @@
       </c>
       <c r="H400"/>
     </row>
-    <row r="401" spans="1:7" customFormat="1" ht="365" hidden="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:7" customFormat="1" ht="365" x14ac:dyDescent="0.2">
       <c r="A401" s="7" t="s">
         <v>440</v>
       </c>
@@ -24143,7 +24142,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="402" spans="1:7" customFormat="1" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:7" customFormat="1" ht="335" x14ac:dyDescent="0.2">
       <c r="A402" s="7" t="s">
         <v>440</v>
       </c>
@@ -24166,7 +24165,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="403" spans="1:7" customFormat="1" ht="380" hidden="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:7" customFormat="1" ht="380" x14ac:dyDescent="0.2">
       <c r="A403" s="7" t="s">
         <v>440</v>
       </c>
@@ -24189,7 +24188,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="404" spans="1:7" customFormat="1" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:7" customFormat="1" ht="288" x14ac:dyDescent="0.2">
       <c r="A404" s="7" t="s">
         <v>440</v>
       </c>
@@ -24212,7 +24211,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="405" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A405" s="7" t="s">
         <v>440</v>
       </c>
@@ -24235,7 +24234,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="406" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A406" s="7" t="s">
         <v>440</v>
       </c>
@@ -24258,7 +24257,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="407" spans="1:7" customFormat="1" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:7" customFormat="1" ht="272" x14ac:dyDescent="0.2">
       <c r="A407" s="7" t="s">
         <v>440</v>
       </c>
@@ -24281,7 +24280,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="408" spans="1:7" customFormat="1" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:7" customFormat="1" ht="288" x14ac:dyDescent="0.2">
       <c r="A408" s="7" t="s">
         <v>440</v>
       </c>
@@ -24304,7 +24303,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="409" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A409" s="7" t="s">
         <v>440</v>
       </c>
@@ -24327,7 +24326,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="410" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A410" s="7" t="s">
         <v>440</v>
       </c>
@@ -24350,7 +24349,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="411" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A411" s="7" t="s">
         <v>440</v>
       </c>
@@ -24373,7 +24372,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="412" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A412" s="7" t="s">
         <v>440</v>
       </c>
@@ -24396,7 +24395,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="413" spans="1:7" customFormat="1" ht="304" hidden="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:7" customFormat="1" ht="304" x14ac:dyDescent="0.2">
       <c r="A413" s="7" t="s">
         <v>440</v>
       </c>
@@ -24419,7 +24418,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="414" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A414" s="7" t="s">
         <v>440</v>
       </c>
@@ -24442,7 +24441,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="415" spans="1:7" customFormat="1" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:7" customFormat="1" ht="320" x14ac:dyDescent="0.2">
       <c r="A415" s="7" t="s">
         <v>440</v>
       </c>
@@ -24465,7 +24464,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="416" spans="1:7" customFormat="1" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:7" customFormat="1" ht="272" x14ac:dyDescent="0.2">
       <c r="A416" s="7" t="s">
         <v>440</v>
       </c>
@@ -24488,7 +24487,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="417" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A417" s="7" t="s">
         <v>440</v>
       </c>
@@ -24512,7 +24511,7 @@
       </c>
       <c r="H417"/>
     </row>
-    <row r="418" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A418" s="7" t="s">
         <v>440</v>
       </c>
@@ -24536,7 +24535,7 @@
       </c>
       <c r="H418"/>
     </row>
-    <row r="419" spans="1:8" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:8" ht="272" x14ac:dyDescent="0.2">
       <c r="A419" s="7" t="s">
         <v>440</v>
       </c>
@@ -24560,7 +24559,7 @@
       </c>
       <c r="H419"/>
     </row>
-    <row r="420" spans="1:8" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:8" ht="240" x14ac:dyDescent="0.2">
       <c r="A420" s="7" t="s">
         <v>440</v>
       </c>
@@ -24584,7 +24583,7 @@
       </c>
       <c r="H420"/>
     </row>
-    <row r="421" spans="1:8" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:8" ht="240" x14ac:dyDescent="0.2">
       <c r="A421" s="7" t="s">
         <v>440</v>
       </c>
@@ -24608,7 +24607,7 @@
       </c>
       <c r="H421"/>
     </row>
-    <row r="422" spans="1:8" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A422" s="7" t="s">
         <v>440</v>
       </c>
@@ -24632,7 +24631,7 @@
       </c>
       <c r="H422"/>
     </row>
-    <row r="423" spans="1:8" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A423" s="7" t="s">
         <v>440</v>
       </c>
@@ -24656,7 +24655,7 @@
       </c>
       <c r="H423"/>
     </row>
-    <row r="424" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A424" s="7" t="s">
         <v>440</v>
       </c>
@@ -24682,7 +24681,7 @@
         <v>2492</v>
       </c>
     </row>
-    <row r="425" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A425" s="7" t="s">
         <v>440</v>
       </c>
@@ -24708,7 +24707,7 @@
         <v>2492</v>
       </c>
     </row>
-    <row r="426" spans="1:8" ht="365" hidden="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:8" ht="365" x14ac:dyDescent="0.2">
       <c r="A426" s="7" t="s">
         <v>440</v>
       </c>
@@ -24732,7 +24731,7 @@
       </c>
       <c r="H426"/>
     </row>
-    <row r="427" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A427" s="7" t="s">
         <v>440</v>
       </c>
@@ -24756,7 +24755,7 @@
       </c>
       <c r="H427"/>
     </row>
-    <row r="428" spans="1:8" ht="365" hidden="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:8" ht="365" x14ac:dyDescent="0.2">
       <c r="A428" s="7" t="s">
         <v>440</v>
       </c>
@@ -24780,7 +24779,7 @@
       </c>
       <c r="H428"/>
     </row>
-    <row r="429" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A429" s="7" t="s">
         <v>440</v>
       </c>
@@ -24804,7 +24803,7 @@
       </c>
       <c r="H429"/>
     </row>
-    <row r="430" spans="1:8" ht="395" hidden="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:8" ht="395" x14ac:dyDescent="0.2">
       <c r="A430" s="7" t="s">
         <v>440</v>
       </c>
@@ -24828,7 +24827,7 @@
       </c>
       <c r="H430"/>
     </row>
-    <row r="431" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A431" s="7" t="s">
         <v>440</v>
       </c>
@@ -24852,7 +24851,7 @@
       </c>
       <c r="H431"/>
     </row>
-    <row r="432" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A432" s="7" t="s">
         <v>440</v>
       </c>
@@ -24876,7 +24875,7 @@
       </c>
       <c r="H432"/>
     </row>
-    <row r="433" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A433" s="7" t="s">
         <v>440</v>
       </c>
@@ -24900,7 +24899,7 @@
       </c>
       <c r="H433"/>
     </row>
-    <row r="434" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A434" s="7" t="s">
         <v>440</v>
       </c>
@@ -24924,7 +24923,7 @@
       </c>
       <c r="H434"/>
     </row>
-    <row r="435" spans="1:8" ht="380" hidden="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:8" ht="380" x14ac:dyDescent="0.2">
       <c r="A435" s="7" t="s">
         <v>440</v>
       </c>
@@ -24948,7 +24947,7 @@
       </c>
       <c r="H435"/>
     </row>
-    <row r="436" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A436" s="7" t="s">
         <v>440</v>
       </c>
@@ -24972,7 +24971,7 @@
       </c>
       <c r="H436"/>
     </row>
-    <row r="437" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A437" s="7" t="s">
         <v>440</v>
       </c>
@@ -24996,7 +24995,7 @@
       </c>
       <c r="H437"/>
     </row>
-    <row r="438" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A438" s="7" t="s">
         <v>440</v>
       </c>
@@ -25020,7 +25019,7 @@
       </c>
       <c r="H438"/>
     </row>
-    <row r="439" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A439" s="7" t="s">
         <v>440</v>
       </c>
@@ -25044,7 +25043,7 @@
       </c>
       <c r="H439"/>
     </row>
-    <row r="440" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A440" s="7" t="s">
         <v>440</v>
       </c>
@@ -25068,7 +25067,7 @@
       </c>
       <c r="H440"/>
     </row>
-    <row r="441" spans="1:8" ht="350" hidden="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:8" ht="350" x14ac:dyDescent="0.2">
       <c r="A441" s="7" t="s">
         <v>440</v>
       </c>
@@ -25092,7 +25091,7 @@
       </c>
       <c r="H441"/>
     </row>
-    <row r="442" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A442" s="7" t="s">
         <v>440</v>
       </c>
@@ -25116,7 +25115,7 @@
       </c>
       <c r="H442"/>
     </row>
-    <row r="443" spans="1:8" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:8" ht="335" x14ac:dyDescent="0.2">
       <c r="A443" s="7" t="s">
         <v>440</v>
       </c>
@@ -25140,7 +25139,7 @@
       </c>
       <c r="H443"/>
     </row>
-    <row r="444" spans="1:8" ht="380" hidden="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:8" ht="380" x14ac:dyDescent="0.2">
       <c r="A444" s="7" t="s">
         <v>440</v>
       </c>
@@ -25164,7 +25163,7 @@
       </c>
       <c r="H444"/>
     </row>
-    <row r="445" spans="1:8" ht="380" hidden="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:8" ht="380" x14ac:dyDescent="0.2">
       <c r="A445" s="7" t="s">
         <v>440</v>
       </c>
@@ -25188,7 +25187,7 @@
       </c>
       <c r="H445"/>
     </row>
-    <row r="446" spans="1:8" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:8" ht="272" x14ac:dyDescent="0.2">
       <c r="A446" s="7" t="s">
         <v>440</v>
       </c>
@@ -25214,7 +25213,7 @@
         <v>2472</v>
       </c>
     </row>
-    <row r="447" spans="1:8" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:8" ht="335" x14ac:dyDescent="0.2">
       <c r="A447" s="7" t="s">
         <v>440</v>
       </c>
@@ -25238,7 +25237,7 @@
       </c>
       <c r="H447"/>
     </row>
-    <row r="448" spans="1:8" ht="395" hidden="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:8" ht="395" x14ac:dyDescent="0.2">
       <c r="A448" s="7" t="s">
         <v>65</v>
       </c>
@@ -25262,7 +25261,7 @@
       </c>
       <c r="H448"/>
     </row>
-    <row r="449" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A449" s="7" t="s">
         <v>440</v>
       </c>
@@ -25286,7 +25285,7 @@
       </c>
       <c r="H449"/>
     </row>
-    <row r="450" spans="1:8" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:8" ht="335" x14ac:dyDescent="0.2">
       <c r="A450" s="7" t="s">
         <v>440</v>
       </c>
@@ -25310,7 +25309,7 @@
       </c>
       <c r="H450"/>
     </row>
-    <row r="451" spans="1:8" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:8" ht="272" x14ac:dyDescent="0.2">
       <c r="A451" s="7" t="s">
         <v>440</v>
       </c>
@@ -25334,7 +25333,7 @@
       </c>
       <c r="H451"/>
     </row>
-    <row r="452" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A452" s="7" t="s">
         <v>440</v>
       </c>
@@ -25360,7 +25359,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="453" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A453" s="7" t="s">
         <v>440</v>
       </c>
@@ -25384,7 +25383,7 @@
       </c>
       <c r="H453"/>
     </row>
-    <row r="454" spans="1:8" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A454" s="7" t="s">
         <v>440</v>
       </c>
@@ -25408,7 +25407,7 @@
       </c>
       <c r="H454"/>
     </row>
-    <row r="455" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A455" s="7" t="s">
         <v>440</v>
       </c>
@@ -25432,7 +25431,7 @@
       </c>
       <c r="H455"/>
     </row>
-    <row r="456" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A456" s="7" t="s">
         <v>440</v>
       </c>
@@ -25456,7 +25455,7 @@
       </c>
       <c r="H456"/>
     </row>
-    <row r="457" spans="1:8" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:8" ht="160" x14ac:dyDescent="0.2">
       <c r="A457" s="7" t="s">
         <v>440</v>
       </c>
@@ -25480,7 +25479,7 @@
       </c>
       <c r="H457"/>
     </row>
-    <row r="458" spans="1:8" ht="395" hidden="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:8" ht="395" x14ac:dyDescent="0.2">
       <c r="A458" s="7" t="s">
         <v>440</v>
       </c>
@@ -25504,7 +25503,7 @@
       </c>
       <c r="H458"/>
     </row>
-    <row r="459" spans="1:8" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:8" ht="320" x14ac:dyDescent="0.2">
       <c r="A459" s="7" t="s">
         <v>440</v>
       </c>
@@ -25528,7 +25527,7 @@
       </c>
       <c r="H459"/>
     </row>
-    <row r="460" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A460" s="7" t="s">
         <v>440</v>
       </c>
@@ -25552,7 +25551,7 @@
       </c>
       <c r="H460"/>
     </row>
-    <row r="461" spans="1:8" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:8" ht="272" x14ac:dyDescent="0.2">
       <c r="A461" s="7" t="s">
         <v>440</v>
       </c>
@@ -25576,7 +25575,7 @@
       </c>
       <c r="H461"/>
     </row>
-    <row r="462" spans="1:8" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:8" ht="335" x14ac:dyDescent="0.2">
       <c r="A462" s="7" t="s">
         <v>440</v>
       </c>
@@ -25600,7 +25599,7 @@
       </c>
       <c r="H462"/>
     </row>
-    <row r="463" spans="1:8" ht="350" hidden="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:8" ht="350" x14ac:dyDescent="0.2">
       <c r="A463" s="7" t="s">
         <v>440</v>
       </c>
@@ -25624,7 +25623,7 @@
       </c>
       <c r="H463"/>
     </row>
-    <row r="464" spans="1:8" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:8" ht="288" x14ac:dyDescent="0.2">
       <c r="A464" s="7" t="s">
         <v>440</v>
       </c>
@@ -25648,7 +25647,7 @@
       </c>
       <c r="H464"/>
     </row>
-    <row r="465" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A465" s="7" t="s">
         <v>440</v>
       </c>
@@ -25671,7 +25670,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="466" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A466" s="7" t="s">
         <v>440</v>
       </c>
@@ -25694,7 +25693,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="467" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A467" s="7" t="s">
         <v>440</v>
       </c>
@@ -25717,7 +25716,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="468" spans="1:7" customFormat="1" ht="350" hidden="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:7" customFormat="1" ht="350" x14ac:dyDescent="0.2">
       <c r="A468" s="7" t="s">
         <v>440</v>
       </c>
@@ -25740,7 +25739,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="469" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A469" s="7" t="s">
         <v>440</v>
       </c>
@@ -25763,7 +25762,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="470" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A470" s="7" t="s">
         <v>440</v>
       </c>
@@ -25786,7 +25785,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="471" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A471" s="7" t="s">
         <v>440</v>
       </c>
@@ -25809,7 +25808,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="472" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A472" s="7" t="s">
         <v>440</v>
       </c>
@@ -25832,7 +25831,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="473" spans="1:7" customFormat="1" ht="128" hidden="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:7" customFormat="1" ht="128" x14ac:dyDescent="0.2">
       <c r="A473" s="7" t="s">
         <v>440</v>
       </c>
@@ -25855,7 +25854,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="474" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A474" s="7" t="s">
         <v>440</v>
       </c>
@@ -25878,7 +25877,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="475" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A475" s="7" t="s">
         <v>440</v>
       </c>
@@ -25901,7 +25900,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="476" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A476" s="7" t="s">
         <v>440</v>
       </c>
@@ -25924,7 +25923,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="477" spans="1:7" customFormat="1" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:7" customFormat="1" ht="335" x14ac:dyDescent="0.2">
       <c r="A477" s="7" t="s">
         <v>440</v>
       </c>
@@ -25947,7 +25946,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="478" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A478" s="7" t="s">
         <v>440</v>
       </c>
@@ -25970,7 +25969,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="479" spans="1:7" customFormat="1" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:7" customFormat="1" ht="144" x14ac:dyDescent="0.2">
       <c r="A479" s="7" t="s">
         <v>440</v>
       </c>
@@ -25993,7 +25992,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="480" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A480" s="7" t="s">
         <v>440</v>
       </c>
@@ -26016,7 +26015,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="481" spans="1:8" ht="380" hidden="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:8" ht="380" x14ac:dyDescent="0.2">
       <c r="A481" s="7" t="s">
         <v>440</v>
       </c>
@@ -26040,7 +26039,7 @@
       </c>
       <c r="H481"/>
     </row>
-    <row r="482" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A482" s="7" t="s">
         <v>440</v>
       </c>
@@ -26064,7 +26063,7 @@
       </c>
       <c r="H482"/>
     </row>
-    <row r="483" spans="1:8" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A483" s="7" t="s">
         <v>440</v>
       </c>
@@ -26088,7 +26087,7 @@
       </c>
       <c r="H483"/>
     </row>
-    <row r="484" spans="1:8" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:8" ht="272" x14ac:dyDescent="0.2">
       <c r="A484" s="7" t="s">
         <v>440</v>
       </c>
@@ -26112,7 +26111,7 @@
       </c>
       <c r="H484"/>
     </row>
-    <row r="485" spans="1:8" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:8" ht="288" x14ac:dyDescent="0.2">
       <c r="A485" s="7" t="s">
         <v>440</v>
       </c>
@@ -26136,7 +26135,7 @@
       </c>
       <c r="H485"/>
     </row>
-    <row r="486" spans="1:8" ht="304" hidden="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:8" ht="304" x14ac:dyDescent="0.2">
       <c r="A486" s="7" t="s">
         <v>440</v>
       </c>
@@ -26160,7 +26159,7 @@
       </c>
       <c r="H486"/>
     </row>
-    <row r="487" spans="1:8" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:8" ht="256" x14ac:dyDescent="0.2">
       <c r="A487" s="7" t="s">
         <v>440</v>
       </c>
@@ -26184,7 +26183,7 @@
       </c>
       <c r="H487"/>
     </row>
-    <row r="488" spans="1:8" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:8" ht="240" x14ac:dyDescent="0.2">
       <c r="A488" s="7" t="s">
         <v>440</v>
       </c>
@@ -26208,7 +26207,7 @@
       </c>
       <c r="H488"/>
     </row>
-    <row r="489" spans="1:8" ht="304" hidden="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:8" ht="304" x14ac:dyDescent="0.2">
       <c r="A489" s="7" t="s">
         <v>440</v>
       </c>
@@ -26232,7 +26231,7 @@
       </c>
       <c r="H489"/>
     </row>
-    <row r="490" spans="1:8" ht="395" hidden="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:8" ht="395" x14ac:dyDescent="0.2">
       <c r="A490" s="7" t="s">
         <v>440</v>
       </c>
@@ -26256,7 +26255,7 @@
       </c>
       <c r="H490"/>
     </row>
-    <row r="491" spans="1:8" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:8" ht="160" x14ac:dyDescent="0.2">
       <c r="A491" s="7" t="s">
         <v>440</v>
       </c>
@@ -26282,7 +26281,7 @@
         <v>2487</v>
       </c>
     </row>
-    <row r="492" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A492" s="7" t="s">
         <v>440</v>
       </c>
@@ -26306,7 +26305,7 @@
       </c>
       <c r="H492"/>
     </row>
-    <row r="493" spans="1:8" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A493" s="7" t="s">
         <v>440</v>
       </c>
@@ -26330,7 +26329,7 @@
       </c>
       <c r="H493"/>
     </row>
-    <row r="494" spans="1:8" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:8" ht="240" x14ac:dyDescent="0.2">
       <c r="A494" s="7" t="s">
         <v>440</v>
       </c>
@@ -26354,7 +26353,7 @@
       </c>
       <c r="H494"/>
     </row>
-    <row r="495" spans="1:8" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A495" s="7" t="s">
         <v>440</v>
       </c>
@@ -26378,7 +26377,7 @@
       </c>
       <c r="H495"/>
     </row>
-    <row r="496" spans="1:8" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:8" ht="288" x14ac:dyDescent="0.2">
       <c r="A496" s="7" t="s">
         <v>440</v>
       </c>
@@ -26402,7 +26401,7 @@
       </c>
       <c r="H496"/>
     </row>
-    <row r="497" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A497" s="7" t="s">
         <v>440</v>
       </c>
@@ -26425,7 +26424,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="498" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A498" s="7" t="s">
         <v>440</v>
       </c>
@@ -26448,7 +26447,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="499" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A499" s="7" t="s">
         <v>440</v>
       </c>
@@ -26471,7 +26470,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="500" spans="1:7" customFormat="1" ht="304" hidden="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:7" customFormat="1" ht="304" x14ac:dyDescent="0.2">
       <c r="A500" s="7" t="s">
         <v>440</v>
       </c>
@@ -26494,7 +26493,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="501" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A501" s="7" t="s">
         <v>440</v>
       </c>
@@ -26517,7 +26516,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="502" spans="1:7" customFormat="1" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:7" customFormat="1" ht="144" x14ac:dyDescent="0.2">
       <c r="A502" s="7" t="s">
         <v>440</v>
       </c>
@@ -26540,7 +26539,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="503" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A503" s="7" t="s">
         <v>440</v>
       </c>
@@ -26563,7 +26562,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="504" spans="1:7" customFormat="1" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:7" customFormat="1" ht="288" x14ac:dyDescent="0.2">
       <c r="A504" s="7" t="s">
         <v>440</v>
       </c>
@@ -26586,7 +26585,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="505" spans="1:7" customFormat="1" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:7" customFormat="1" ht="288" x14ac:dyDescent="0.2">
       <c r="A505" s="7" t="s">
         <v>440</v>
       </c>
@@ -26609,7 +26608,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="506" spans="1:7" customFormat="1" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:7" customFormat="1" ht="144" x14ac:dyDescent="0.2">
       <c r="A506" s="7" t="s">
         <v>440</v>
       </c>
@@ -26632,7 +26631,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="507" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A507" s="7" t="s">
         <v>440</v>
       </c>
@@ -26655,7 +26654,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="508" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A508" s="7" t="s">
         <v>440</v>
       </c>
@@ -26678,7 +26677,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="509" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A509" s="7" t="s">
         <v>440</v>
       </c>
@@ -26701,7 +26700,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="510" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A510" s="7" t="s">
         <v>440</v>
       </c>
@@ -26724,7 +26723,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="511" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A511" s="7" t="s">
         <v>440</v>
       </c>
@@ -26747,7 +26746,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="512" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A512" s="7" t="s">
         <v>440</v>
       </c>
@@ -26770,7 +26769,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="513" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A513" s="7" t="s">
         <v>440</v>
       </c>
@@ -26793,7 +26792,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="514" spans="1:7" customFormat="1" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:7" customFormat="1" ht="272" x14ac:dyDescent="0.2">
       <c r="A514" s="7" t="s">
         <v>440</v>
       </c>
@@ -26816,7 +26815,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="515" spans="1:7" customFormat="1" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:7" customFormat="1" ht="272" x14ac:dyDescent="0.2">
       <c r="A515" s="7" t="s">
         <v>440</v>
       </c>
@@ -26839,7 +26838,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="516" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A516" s="7" t="s">
         <v>440</v>
       </c>
@@ -26862,7 +26861,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="517" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A517" s="7" t="s">
         <v>440</v>
       </c>
@@ -26885,7 +26884,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="518" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A518" s="7" t="s">
         <v>440</v>
       </c>
@@ -26908,7 +26907,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="519" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A519" s="7" t="s">
         <v>440</v>
       </c>
@@ -26931,7 +26930,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="520" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A520" s="7" t="s">
         <v>440</v>
       </c>
@@ -26954,7 +26953,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="521" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A521" s="7" t="s">
         <v>440</v>
       </c>
@@ -26977,7 +26976,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="522" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A522" s="7" t="s">
         <v>440</v>
       </c>
@@ -27000,7 +26999,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="523" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A523" s="7" t="s">
         <v>440</v>
       </c>
@@ -27023,7 +27022,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="524" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A524" s="7" t="s">
         <v>440</v>
       </c>
@@ -27046,7 +27045,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="525" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A525" s="7" t="s">
         <v>440</v>
       </c>
@@ -27069,7 +27068,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="526" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A526" s="7" t="s">
         <v>440</v>
       </c>
@@ -27092,7 +27091,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="527" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A527" s="7" t="s">
         <v>440</v>
       </c>
@@ -27115,7 +27114,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="528" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A528" s="7" t="s">
         <v>440</v>
       </c>
@@ -27138,7 +27137,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="529" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A529" s="7" t="s">
         <v>440</v>
       </c>
@@ -27161,7 +27160,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="530" spans="1:7" customFormat="1" ht="350" hidden="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:7" customFormat="1" ht="350" x14ac:dyDescent="0.2">
       <c r="A530" s="7" t="s">
         <v>65</v>
       </c>
@@ -27184,7 +27183,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="531" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A531" s="7" t="s">
         <v>440</v>
       </c>
@@ -27207,7 +27206,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="532" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A532" s="7" t="s">
         <v>440</v>
       </c>
@@ -27230,7 +27229,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="533" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A533" s="7" t="s">
         <v>440</v>
       </c>
@@ -27253,7 +27252,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="534" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A534" s="7" t="s">
         <v>65</v>
       </c>
@@ -27276,7 +27275,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="535" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A535" s="7" t="s">
         <v>440</v>
       </c>
@@ -27299,7 +27298,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="536" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A536" s="7" t="s">
         <v>440</v>
       </c>
@@ -27322,7 +27321,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="537" spans="1:7" customFormat="1" ht="395" hidden="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:7" customFormat="1" ht="395" x14ac:dyDescent="0.2">
       <c r="A537" s="7" t="s">
         <v>65</v>
       </c>
@@ -27345,7 +27344,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="538" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A538" s="7" t="s">
         <v>440</v>
       </c>
@@ -27368,7 +27367,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="539" spans="1:7" customFormat="1" ht="160" hidden="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:7" customFormat="1" ht="160" x14ac:dyDescent="0.2">
       <c r="A539" s="7" t="s">
         <v>440</v>
       </c>
@@ -27391,7 +27390,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="540" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A540" s="7" t="s">
         <v>440</v>
       </c>
@@ -27414,7 +27413,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="541" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A541" s="7" t="s">
         <v>440</v>
       </c>
@@ -27437,7 +27436,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="542" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A542" s="7" t="s">
         <v>440</v>
       </c>
@@ -27460,7 +27459,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="543" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A543" s="7" t="s">
         <v>440</v>
       </c>
@@ -27483,7 +27482,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="544" spans="1:7" customFormat="1" ht="304" hidden="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:7" customFormat="1" ht="304" x14ac:dyDescent="0.2">
       <c r="A544" s="7" t="s">
         <v>440</v>
       </c>
@@ -27506,7 +27505,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="545" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A545" s="7" t="s">
         <v>440</v>
       </c>
@@ -27530,7 +27529,7 @@
       </c>
       <c r="H545"/>
     </row>
-    <row r="546" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A546" s="7" t="s">
         <v>440</v>
       </c>
@@ -27556,7 +27555,7 @@
         <v>2477</v>
       </c>
     </row>
-    <row r="547" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A547" s="7" t="s">
         <v>440</v>
       </c>
@@ -27580,7 +27579,7 @@
       </c>
       <c r="H547"/>
     </row>
-    <row r="548" spans="1:8" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:8" ht="256" x14ac:dyDescent="0.2">
       <c r="A548" s="7" t="s">
         <v>440</v>
       </c>
@@ -27604,7 +27603,7 @@
       </c>
       <c r="H548"/>
     </row>
-    <row r="549" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A549" s="7" t="s">
         <v>65</v>
       </c>
@@ -27630,7 +27629,7 @@
         <v>2479</v>
       </c>
     </row>
-    <row r="550" spans="1:8" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A550" s="7" t="s">
         <v>440</v>
       </c>
@@ -27654,7 +27653,7 @@
       </c>
       <c r="H550"/>
     </row>
-    <row r="551" spans="1:8" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:8" ht="256" x14ac:dyDescent="0.2">
       <c r="A551" s="7" t="s">
         <v>440</v>
       </c>
@@ -27678,7 +27677,7 @@
       </c>
       <c r="H551"/>
     </row>
-    <row r="552" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A552" s="7" t="s">
         <v>440</v>
       </c>
@@ -27702,7 +27701,7 @@
       </c>
       <c r="H552"/>
     </row>
-    <row r="553" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A553" s="7" t="s">
         <v>440</v>
       </c>
@@ -27726,7 +27725,7 @@
       </c>
       <c r="H553"/>
     </row>
-    <row r="554" spans="1:8" ht="395" hidden="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:8" ht="395" x14ac:dyDescent="0.2">
       <c r="A554" s="7" t="s">
         <v>65</v>
       </c>
@@ -27750,7 +27749,7 @@
       </c>
       <c r="H554"/>
     </row>
-    <row r="555" spans="1:8" ht="350" hidden="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:8" ht="350" x14ac:dyDescent="0.2">
       <c r="A555" s="7" t="s">
         <v>440</v>
       </c>
@@ -27774,7 +27773,7 @@
       </c>
       <c r="H555"/>
     </row>
-    <row r="556" spans="1:8" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:8" ht="256" x14ac:dyDescent="0.2">
       <c r="A556" s="7" t="s">
         <v>440</v>
       </c>
@@ -27798,7 +27797,7 @@
       </c>
       <c r="H556"/>
     </row>
-    <row r="557" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A557" s="7" t="s">
         <v>440</v>
       </c>
@@ -27822,7 +27821,7 @@
       </c>
       <c r="H557"/>
     </row>
-    <row r="558" spans="1:8" ht="380" hidden="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:8" ht="380" x14ac:dyDescent="0.2">
       <c r="A558" s="7" t="s">
         <v>440</v>
       </c>
@@ -27846,7 +27845,7 @@
       </c>
       <c r="H558"/>
     </row>
-    <row r="559" spans="1:8" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:8" ht="272" x14ac:dyDescent="0.2">
       <c r="A559" s="7" t="s">
         <v>440</v>
       </c>
@@ -27870,7 +27869,7 @@
       </c>
       <c r="H559"/>
     </row>
-    <row r="560" spans="1:8" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:8" ht="272" x14ac:dyDescent="0.2">
       <c r="A560" s="7" t="s">
         <v>440</v>
       </c>
@@ -27894,7 +27893,7 @@
       </c>
       <c r="H560"/>
     </row>
-    <row r="561" spans="1:7" customFormat="1" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:7" customFormat="1" ht="335" x14ac:dyDescent="0.2">
       <c r="A561" s="7" t="s">
         <v>440</v>
       </c>
@@ -27917,7 +27916,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="562" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A562" s="7" t="s">
         <v>440</v>
       </c>
@@ -27940,7 +27939,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="563" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A563" s="7" t="s">
         <v>440</v>
       </c>
@@ -27963,7 +27962,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="564" spans="1:7" customFormat="1" ht="395" hidden="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:7" customFormat="1" ht="395" x14ac:dyDescent="0.2">
       <c r="A564" s="7" t="s">
         <v>65</v>
       </c>
@@ -27986,7 +27985,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="565" spans="1:7" customFormat="1" ht="365" hidden="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:7" customFormat="1" ht="365" x14ac:dyDescent="0.2">
       <c r="A565" s="7" t="s">
         <v>440</v>
       </c>
@@ -28009,7 +28008,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="566" spans="1:7" customFormat="1" ht="365" hidden="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:7" customFormat="1" ht="365" x14ac:dyDescent="0.2">
       <c r="A566" s="7" t="s">
         <v>440</v>
       </c>
@@ -28032,7 +28031,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="567" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A567" s="7" t="s">
         <v>440</v>
       </c>
@@ -28055,7 +28054,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="568" spans="1:7" customFormat="1" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:7" customFormat="1" ht="335" x14ac:dyDescent="0.2">
       <c r="A568" s="7" t="s">
         <v>440</v>
       </c>
@@ -28078,7 +28077,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="569" spans="1:7" customFormat="1" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:7" customFormat="1" ht="335" x14ac:dyDescent="0.2">
       <c r="A569" s="7" t="s">
         <v>440</v>
       </c>
@@ -28101,7 +28100,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="570" spans="1:7" customFormat="1" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:7" customFormat="1" ht="335" x14ac:dyDescent="0.2">
       <c r="A570" s="7" t="s">
         <v>440</v>
       </c>
@@ -28124,7 +28123,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="571" spans="1:7" customFormat="1" ht="380" hidden="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:7" customFormat="1" ht="380" x14ac:dyDescent="0.2">
       <c r="A571" s="7" t="s">
         <v>440</v>
       </c>
@@ -28147,7 +28146,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="572" spans="1:7" customFormat="1" ht="304" hidden="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:7" customFormat="1" ht="304" x14ac:dyDescent="0.2">
       <c r="A572" s="7" t="s">
         <v>440</v>
       </c>
@@ -28170,7 +28169,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="573" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A573" s="7" t="s">
         <v>440</v>
       </c>
@@ -28193,7 +28192,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="574" spans="1:7" customFormat="1" ht="365" hidden="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:7" customFormat="1" ht="365" x14ac:dyDescent="0.2">
       <c r="A574" s="7" t="s">
         <v>440</v>
       </c>
@@ -28216,7 +28215,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="575" spans="1:7" customFormat="1" ht="350" hidden="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:7" customFormat="1" ht="350" x14ac:dyDescent="0.2">
       <c r="A575" s="7" t="s">
         <v>440</v>
       </c>
@@ -28239,7 +28238,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="576" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A576" s="7" t="s">
         <v>440</v>
       </c>
@@ -28262,7 +28261,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="577" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A577" s="7" t="s">
         <v>440</v>
       </c>
@@ -28285,7 +28284,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="578" spans="1:7" customFormat="1" ht="380" hidden="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:7" customFormat="1" ht="380" x14ac:dyDescent="0.2">
       <c r="A578" s="7" t="s">
         <v>440</v>
       </c>
@@ -28308,7 +28307,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="579" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A579" s="7" t="s">
         <v>440</v>
       </c>
@@ -28331,7 +28330,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="580" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A580" s="7" t="s">
         <v>440</v>
       </c>
@@ -28354,7 +28353,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="581" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A581" s="7" t="s">
         <v>440</v>
       </c>
@@ -28377,7 +28376,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="582" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A582" s="7" t="s">
         <v>440</v>
       </c>
@@ -28400,7 +28399,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="583" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A583" s="7" t="s">
         <v>440</v>
       </c>
@@ -28423,7 +28422,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="584" spans="1:7" customFormat="1" ht="192" hidden="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:7" customFormat="1" ht="192" x14ac:dyDescent="0.2">
       <c r="A584" s="7" t="s">
         <v>440</v>
       </c>
@@ -28446,7 +28445,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="585" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A585" s="7" t="s">
         <v>440</v>
       </c>
@@ -28469,7 +28468,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="586" spans="1:7" customFormat="1" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:7" customFormat="1" ht="320" x14ac:dyDescent="0.2">
       <c r="A586" s="7" t="s">
         <v>440</v>
       </c>
@@ -28492,7 +28491,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="587" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A587" s="7" t="s">
         <v>440</v>
       </c>
@@ -28515,7 +28514,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="588" spans="1:7" customFormat="1" ht="304" hidden="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:7" customFormat="1" ht="304" x14ac:dyDescent="0.2">
       <c r="A588" s="7" t="s">
         <v>440</v>
       </c>
@@ -28538,7 +28537,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="589" spans="1:7" customFormat="1" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:7" customFormat="1" ht="320" x14ac:dyDescent="0.2">
       <c r="A589" s="7" t="s">
         <v>440</v>
       </c>
@@ -28561,7 +28560,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="590" spans="1:7" customFormat="1" ht="335" hidden="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:7" customFormat="1" ht="335" x14ac:dyDescent="0.2">
       <c r="A590" s="7" t="s">
         <v>440</v>
       </c>
@@ -28584,7 +28583,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="591" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A591" s="7" t="s">
         <v>440</v>
       </c>
@@ -28607,7 +28606,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="592" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A592" s="7" t="s">
         <v>440</v>
       </c>
@@ -28630,7 +28629,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="593" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A593" s="7" t="s">
         <v>440</v>
       </c>
@@ -28653,7 +28652,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="594" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A594" s="7" t="s">
         <v>440</v>
       </c>
@@ -28676,7 +28675,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="595" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A595" s="7" t="s">
         <v>440</v>
       </c>
@@ -28699,7 +28698,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="596" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A596" s="7" t="s">
         <v>440</v>
       </c>
@@ -28722,7 +28721,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="597" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A597" s="7" t="s">
         <v>440</v>
       </c>
@@ -28745,7 +28744,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="598" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A598" s="7" t="s">
         <v>440</v>
       </c>
@@ -28768,7 +28767,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="599" spans="1:7" customFormat="1" ht="365" hidden="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:7" customFormat="1" ht="365" x14ac:dyDescent="0.2">
       <c r="A599" s="7" t="s">
         <v>440</v>
       </c>
@@ -28791,7 +28790,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="600" spans="1:7" customFormat="1" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:7" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A600" s="7" t="s">
         <v>440</v>
       </c>
@@ -28814,7 +28813,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="601" spans="1:7" customFormat="1" ht="304" hidden="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:7" customFormat="1" ht="304" x14ac:dyDescent="0.2">
       <c r="A601" s="7" t="s">
         <v>440</v>
       </c>
@@ -28837,7 +28836,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="602" spans="1:7" customFormat="1" ht="350" hidden="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:7" customFormat="1" ht="350" x14ac:dyDescent="0.2">
       <c r="A602" s="7" t="s">
         <v>440</v>
       </c>
@@ -28860,7 +28859,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="603" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A603" s="7" t="s">
         <v>440</v>
       </c>
@@ -28883,7 +28882,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="604" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A604" s="7" t="s">
         <v>440</v>
       </c>
@@ -28906,7 +28905,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="605" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A605" s="7" t="s">
         <v>440</v>
       </c>
@@ -28929,7 +28928,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="606" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A606" s="7" t="s">
         <v>440</v>
       </c>
@@ -28952,7 +28951,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="607" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A607" s="7" t="s">
         <v>440</v>
       </c>
@@ -28975,7 +28974,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="608" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A608" s="7" t="s">
         <v>440</v>
       </c>
@@ -28998,7 +28997,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="609" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A609" s="7" t="s">
         <v>440</v>
       </c>
@@ -29021,7 +29020,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="610" spans="1:7" customFormat="1" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:7" customFormat="1" ht="272" x14ac:dyDescent="0.2">
       <c r="A610" s="7" t="s">
         <v>440</v>
       </c>
@@ -29044,7 +29043,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="611" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A611" s="7" t="s">
         <v>440</v>
       </c>
@@ -29067,7 +29066,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="612" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A612" s="7" t="s">
         <v>440</v>
       </c>
@@ -29090,7 +29089,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="613" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A613" s="7" t="s">
         <v>440</v>
       </c>
@@ -29113,7 +29112,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="614" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A614" s="7" t="s">
         <v>440</v>
       </c>
@@ -29136,7 +29135,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="615" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A615" s="7" t="s">
         <v>440</v>
       </c>
@@ -29159,7 +29158,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="616" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A616" s="7" t="s">
         <v>440</v>
       </c>
@@ -29182,7 +29181,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="617" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A617" s="7" t="s">
         <v>440</v>
       </c>
@@ -29205,7 +29204,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="618" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A618" s="7" t="s">
         <v>440</v>
       </c>
@@ -29228,7 +29227,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="619" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A619" s="7" t="s">
         <v>440</v>
       </c>
@@ -29251,7 +29250,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="620" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A620" s="7" t="s">
         <v>440</v>
       </c>
@@ -29274,7 +29273,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="621" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A621" s="7" t="s">
         <v>440</v>
       </c>
@@ -29297,7 +29296,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="622" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A622" s="7" t="s">
         <v>440</v>
       </c>
@@ -29320,7 +29319,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="623" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A623" s="7" t="s">
         <v>440</v>
       </c>
@@ -29343,7 +29342,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="624" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A624" s="7" t="s">
         <v>440</v>
       </c>
@@ -29366,7 +29365,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="625" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A625" s="7" t="s">
         <v>440</v>
       </c>
@@ -29389,7 +29388,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="626" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A626" s="7" t="s">
         <v>440</v>
       </c>
@@ -29412,7 +29411,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="627" spans="1:7" customFormat="1" ht="304" hidden="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:7" customFormat="1" ht="304" x14ac:dyDescent="0.2">
       <c r="A627" s="7" t="s">
         <v>440</v>
       </c>
@@ -29435,7 +29434,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="628" spans="1:7" customFormat="1" ht="320" hidden="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:7" customFormat="1" ht="320" x14ac:dyDescent="0.2">
       <c r="A628" s="7" t="s">
         <v>440</v>
       </c>
@@ -29458,7 +29457,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="629" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A629" s="7" t="s">
         <v>440</v>
       </c>
@@ -29481,7 +29480,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="630" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A630" s="7" t="s">
         <v>440</v>
       </c>
@@ -29504,7 +29503,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="631" spans="1:7" customFormat="1" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:7" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A631" s="7" t="s">
         <v>440</v>
       </c>
@@ -29527,7 +29526,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="632" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A632" s="7" t="s">
         <v>440</v>
       </c>
@@ -29550,7 +29549,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="633" spans="1:7" customFormat="1" ht="256" hidden="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:7" customFormat="1" ht="256" x14ac:dyDescent="0.2">
       <c r="A633" s="7" t="s">
         <v>440</v>
       </c>
@@ -29573,7 +29572,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="634" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A634" s="7" t="s">
         <v>440</v>
       </c>
@@ -29596,7 +29595,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="635" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A635" s="7" t="s">
         <v>440</v>
       </c>
@@ -29619,7 +29618,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="636" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A636" s="7" t="s">
         <v>440</v>
       </c>
@@ -29642,7 +29641,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="637" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A637" s="7" t="s">
         <v>440</v>
       </c>
@@ -29665,7 +29664,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="638" spans="1:7" customFormat="1" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:7" customFormat="1" ht="240" x14ac:dyDescent="0.2">
       <c r="A638" s="7" t="s">
         <v>440</v>
       </c>
@@ -29688,7 +29687,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="639" spans="1:7" customFormat="1" ht="176" hidden="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:7" customFormat="1" ht="176" x14ac:dyDescent="0.2">
       <c r="A639" s="7" t="s">
         <v>440</v>
       </c>
@@ -29711,7 +29710,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="640" spans="1:7" customFormat="1" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:7" customFormat="1" ht="208" x14ac:dyDescent="0.2">
       <c r="A640" s="7" t="s">
         <v>440</v>
       </c>
@@ -29734,7 +29733,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="641" spans="1:8" ht="208" hidden="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:8" ht="208" x14ac:dyDescent="0.2">
       <c r="A641" s="7" t="s">
         <v>440</v>
       </c>
@@ -29758,7 +29757,7 @@
       </c>
       <c r="H641"/>
     </row>
-    <row r="642" spans="1:8" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:8" ht="144" x14ac:dyDescent="0.2">
       <c r="A642" s="7" t="s">
         <v>440</v>
       </c>
@@ -29782,7 +29781,7 @@
       </c>
       <c r="H642"/>
     </row>
-    <row r="643" spans="1:8" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:8" ht="288" x14ac:dyDescent="0.2">
       <c r="A643" s="7" t="s">
         <v>440</v>
       </c>
@@ -29806,7 +29805,7 @@
       </c>
       <c r="H643"/>
     </row>
-    <row r="644" spans="1:8" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:8" ht="288" x14ac:dyDescent="0.2">
       <c r="A644" s="7" t="s">
         <v>440</v>
       </c>
@@ -29830,7 +29829,7 @@
       </c>
       <c r="H644"/>
     </row>
-    <row r="645" spans="1:8" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A645" s="7" t="s">
         <v>440</v>
       </c>
@@ -29854,7 +29853,7 @@
       </c>
       <c r="H645"/>
     </row>
-    <row r="646" spans="1:8" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A646" s="7" t="s">
         <v>440</v>
       </c>
@@ -29878,7 +29877,7 @@
       </c>
       <c r="H646"/>
     </row>
-    <row r="647" spans="1:8" ht="128" hidden="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:8" ht="128" x14ac:dyDescent="0.2">
       <c r="A647" s="7" t="s">
         <v>440</v>
       </c>
@@ -29902,7 +29901,7 @@
       </c>
       <c r="H647"/>
     </row>
-    <row r="648" spans="1:8" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A648" s="7" t="s">
         <v>440</v>
       </c>
@@ -29928,7 +29927,7 @@
         <v>2576</v>
       </c>
     </row>
-    <row r="649" spans="1:8" ht="288" hidden="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:8" ht="288" x14ac:dyDescent="0.2">
       <c r="A649" s="7" t="s">
         <v>440</v>
       </c>
@@ -29952,7 +29951,7 @@
       </c>
       <c r="H649"/>
     </row>
-    <row r="650" spans="1:8" ht="144" hidden="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:8" ht="144" x14ac:dyDescent="0.2">
       <c r="A650" s="7" t="s">
         <v>440</v>
       </c>
@@ -29976,7 +29975,7 @@
       </c>
       <c r="H650"/>
     </row>
-    <row r="651" spans="1:8" ht="240" hidden="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:8" ht="240" x14ac:dyDescent="0.2">
       <c r="A651" s="7" t="s">
         <v>440</v>
       </c>
@@ -30000,7 +29999,7 @@
       </c>
       <c r="H651"/>
     </row>
-    <row r="652" spans="1:8" ht="224" hidden="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A652" s="7" t="s">
         <v>440</v>
       </c>
@@ -30024,7 +30023,7 @@
       </c>
       <c r="H652"/>
     </row>
-    <row r="653" spans="1:8" ht="304" hidden="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:8" ht="304" x14ac:dyDescent="0.2">
       <c r="A653" s="7" t="s">
         <v>440</v>
       </c>
@@ -30048,7 +30047,7 @@
       </c>
       <c r="H653"/>
     </row>
-    <row r="654" spans="1:8" ht="272" hidden="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:8" ht="272" x14ac:dyDescent="0.2">
       <c r="A654" s="7" t="s">
         <v>440</v>
       </c>
@@ -30073,30 +30072,7 @@
       <c r="H654"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ref="A1:H654" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x14">
-          <filters>
-            <x14:filter val="Set the following parameters in `/etc/sysctl.conf` or a `/etc/sysctl.d/*` _x000a_file:_x000a__x000a__Example:__x000a_```_x000a_# printf &quot;_x000a_net.ipv4.conf.all.accept_source_route = _x000a_0_x000a_net.ipv4.conf.default.accept_source_route = 0_x000a_&quot; &gt;&gt; _x000a_/etc/sysctl.d/60-netipv4_sysctl.conf_x000a_```_x000a__x000a_Run the following command to set the _x000a_active kernel parameters:_x000a_```_x000a_# {_x000a_ sysctl -w _x000a_net.ipv4.conf.all.accept_source_route=0_x000a_ sysctl -w _x000a_net.ipv4.conf.default.accept_source_route=0_x000a_ sysctl -w _x000a_net.ipv4.route.flush=1_x000a_}_x000a_```_x000a__x000a_**IF** IPv6 is enabled on the system:_x000a__x000a_Set the _x000a_following parameters in `/etc/sysctl.conf` or a `/etc/sysctl.d/*` _x000a_file:_x000a__x000a__Example:__x000a_```_x000a_# printf &quot;_x000a_net.ipv6.conf.all.accept_source_route = _x000a_0_x000a_net.ipv6.conf.default.accept_source_route = 0_x000a_&quot; &gt;&gt; _x000a_/etc/sysctl.d/60-netipv6_sysctl.conf_x000a_```_x000a__x000a_Run the following command to set the _x000a_active kernel parameters:_x000a_```_x000a_# {_x000a_ sysctl -w _x000a_net.ipv6.conf.all.accept_source_route=0_x000a_ sysctl -w _x000a_net.ipv6.conf.default.accept_source_route=0_x000a_ sysctl -w _x000a_net.ipv6.route.flush=1_x000a_}_x000a_```"/>
-            <x14:filter val="Set the following parameters in `/etc/sysctl.conf` or a `/etc/sysctl.d/*` _x000a_file:_x000a__x000a__Example:__x000a_```_x000a_# printf &quot;_x000a_net.ipv4.conf.all.log_martians = _x000a_1_x000a_net.ipv4.conf.default.log_martians = 1_x000a_&quot; &gt;&gt; _x000a_/etc/sysctl.d/60-netipv4_sysctl.conf_x000a_```_x000a__x000a_Run the following command to set the _x000a_active kernel parameters:_x000a__x000a_```_x000a_# {_x000a_ sysctl -w net.ipv4.conf.all.log_martians=1_x000a_ _x000a_sysctl -w net.ipv4.conf.default.log_martians=1_x000a_ sysctl -w _x000a_net.ipv4.route.flush=1_x000a_}_x000a_```"/>
-            <x14:filter val="Set the following parameters in `/etc/sysctl.conf` or a `/etc/sysctl.d/*` _x000a_file:_x000a__x000a__Example:__x000a_```_x000a_# printf &quot;_x000a_net.ipv4.conf.all.send_redirects = _x000a_0_x000a_net.ipv4.conf.default.send_redirects = 0_x000a_&quot; &gt;&gt; _x000a_/etc/sysctl.d/60-netipv4_sysctl.conf_x000a_```_x000a__x000a_Run the following command to set the _x000a_active kernel parameters:_x000a__x000a_```_x000a_# {_x000a_ sysctl -w _x000a_net.ipv4.conf.all.send_redirects=0_x000a_ sysctl -w _x000a_net.ipv4.conf.default.send_redirects=0_x000a_ sysctl -w net.ipv4.route.flush=1_x000a_}_x000a_```"/>
-            <x14:filter val="Verify RHEL 9 does not accept IPv4 source-routed packets by default._x000a__x000a_Check the value of the accept source route variable with the following command:_x000a__x000a_$ sudo sysctl net.ipv4.conf.default.accept_source_route_x000a__x000a_net.ipv4.conf.default.accept_source_route = 0_x000a__x000a_If the returned line does not have a value of &quot;0&quot;, a line is not returned, or the line is commented out, this is a finding._x000a__x000a_Check that the configuration files are present to enable this network parameter._x000a__x000a_$ sudo /usr/lib/systemd/systemd-sysctl --cat-config | egrep -v '^(#|;)' | grep -F net.ipv4.conf.default.accept_source_route | tail -1_x000a__x000a_net.ipv4.conf.default.accept_source_route = 0_x000a__x000a_If &quot;net.ipv4.conf.default.accept_source_route&quot; is not set to &quot;0&quot; or is missing, this is a finding."/>
-            <x14:filter val="Verify RHEL 9 is not performing IPv4 packet forwarding, unless the system is a router._x000a__x000a_Check that IPv4 forwarding is disabled using the following command:_x000a__x000a_$ sudo sysctl net.ipv4.conf.all.forwarding_x000a__x000a_net.ipv4.conf.all.forwarding = 0_x000a__x000a_If the IPv4 forwarding value is not &quot;0&quot; and is not documented with the information system security officer (ISSO) as an operational requirement, this is a finding._x000a__x000a_Check that the configuration files are present to enable this network parameter._x000a__x000a_$ sudo (/usr/lib/systemd/systemd-sysctl --cat-config; cat /etc/sysctl.conf) | egrep -v '^(#|$)' | grep net.ipv4.conf.all.forwarding | tail -1_x000a__x000a_net.ipv4.conf.all.forwarding = 0_x000a__x000a_If &quot;net.ipv4.conf.all.forwarding&quot; is not set to &quot;0&quot; and is not documented with the ISSO as an operational requirement or is missing, this is a finding."/>
-            <x14:filter val="Verify RHEL 9 logs IPv4 martian packets by default._x000a__x000a_Check the value of the accept source route variable with the following command:_x000a__x000a_$ sudo sysctl net.ipv4.conf.default.log_martians_x000a__x000a_net.ipv4.conf.default.log_martians = 1_x000a__x000a_If the returned line does not have a value of &quot;1&quot;, a line is not returned, or the line is commented out, this is a finding._x000a__x000a_Check that the configuration files are present to enable this network parameter._x000a__x000a_$ sudo /usr/lib/systemd/systemd-sysctl --cat-config | egrep -v '^(#|;)' | grep -F net.ipv4.conf.default.log_martians | tail -1_x000a__x000a_net.ipv4.conf.default.log_martians = 1_x000a__x000a_If &quot;net.ipv4.conf.default.log_martians&quot; is not set to &quot;1&quot; or is missing, this is a finding."/>
-            <x14:filter val="Verify RHEL 9 logs IPv4 martian packets._x000a__x000a_Check the value of the accept source route variable with the following command:_x000a__x000a_$ sudo sysctl net.ipv4.conf.all.log_martians_x000a__x000a_net.ipv4.conf.all.log_martians = 1_x000a__x000a_If the returned line does not have a value of &quot;1&quot;, a line is not returned, or the line is commented out, this is a finding._x000a__x000a_Check that the configuration files are present to enable this network parameter._x000a__x000a_$ sudo /usr/lib/systemd/systemd-sysctl --cat-config | egrep -v '^(#|;)' | grep -F net.ipv4.conf.all.log_martians | tail -1_x000a__x000a_net.ipv4.conf.all.log_martians = 1_x000a__x000a_If &quot;net.ipv4.conf.all.log_martians&quot; is not set to &quot;1&quot; or is missing, this is a finding."/>
-            <x14:filter val="Verify RHEL 9 will not accept IPv4 source-routed packets._x000a__x000a_Check the value of the all &quot;accept_source_route&quot; variables with the following command:_x000a__x000a_$ sudo sysctl net.ipv4.conf.all.accept_source_route_x000a__x000a_net.ipv4.conf.all.accept_source_route = 0_x000a__x000a_If the returned line does not have a value of &quot;0&quot;, a line is not returned, or the line is commented out, this is a finding._x000a__x000a_Check that the configuration files are present to enable this network parameter._x000a__x000a_$ sudo /usr/lib/systemd/systemd-sysctl --cat-config | egrep -v '^(#|;)' | grep -F net.ipv4.conf.all.accept_source_route | tail -1_x000a__x000a_net.ipv4.conf.all.accept_source_route = 0_x000a__x000a_If &quot;net.ipv4.conf.all.accept_source_route&quot; is not set to &quot;0&quot; or is missing, this is a finding."/>
-          </filters>
-        </mc:Choice>
-        <mc:Fallback>
-          <customFilters>
-            <customFilter val=""/>
-            <customFilter operator="notEqual" val=" "/>
-          </customFilters>
-        </mc:Fallback>
-      </mc:AlternateContent>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H654" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Aptos"&amp;11&amp;K000000 NONCONFIDENTIAL // EXTERNAL&amp;1#_x000D_</oddHeader>
